--- a/assets/Listados/CTSM - 3458742 - 2026.xlsx
+++ b/assets/Listados/CTSM - 3458742 - 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Carlos\Documents\Bot_sena_seguimiento\assets\Listados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0489370-6B8D-48D7-A646-6BA8C5C29061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCE4E5F7-20D8-4874-AD48-E25D66BB1BDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/assets/Listados/CTSM - 3458742 - 2026.xlsx
+++ b/assets/Listados/CTSM - 3458742 - 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Carlos\Documents\Bot_sena_seguimiento\assets\Listados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCE4E5F7-20D8-4874-AD48-E25D66BB1BDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F6DA3C6-B69C-43FC-9B08-A79249FDF0DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -165,7 +165,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="290">
   <si>
     <r>
       <rPr>
@@ -2846,6 +2846,22 @@
     <xf numFmtId="0" fontId="37" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="15" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="59" fillId="15" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="15" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3031,41 +3047,6 @@
     <xf numFmtId="0" fontId="39" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="13" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="50" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="74" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3084,25 +3065,44 @@
     <xf numFmtId="0" fontId="43" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="39" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="15" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="59" fillId="15" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="13" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="50" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="15" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -4495,125 +4495,125 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:129" ht="24.75" customHeight="1">
-      <c r="A1" s="154"/>
-      <c r="B1" s="155"/>
-      <c r="C1" s="158" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="104"/>
-      <c r="E1" s="104"/>
-      <c r="F1" s="155"/>
-      <c r="G1" s="134" t="s">
+      <c r="A1" s="162"/>
+      <c r="B1" s="163"/>
+      <c r="C1" s="166" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="112"/>
+      <c r="E1" s="112"/>
+      <c r="F1" s="163"/>
+      <c r="G1" s="142" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
-      <c r="M1" s="88"/>
-      <c r="N1" s="88"/>
-      <c r="O1" s="88"/>
-      <c r="P1" s="141"/>
-      <c r="Q1" s="88"/>
-      <c r="R1" s="88"/>
-      <c r="S1" s="138"/>
-      <c r="T1" s="142"/>
-      <c r="U1" s="83"/>
-      <c r="V1" s="83"/>
-      <c r="W1" s="83"/>
-      <c r="X1" s="143"/>
-      <c r="Y1" s="83"/>
-      <c r="Z1" s="83"/>
-      <c r="AA1" s="83"/>
-      <c r="AB1" s="142"/>
-      <c r="AC1" s="83"/>
-      <c r="AD1" s="83"/>
-      <c r="AE1" s="83"/>
-      <c r="AF1" s="83"/>
-      <c r="AG1" s="83"/>
-      <c r="AH1" s="83"/>
-      <c r="AI1" s="83"/>
-      <c r="AJ1" s="83"/>
-      <c r="AK1" s="86"/>
-      <c r="AL1" s="82"/>
-      <c r="AM1" s="83"/>
-      <c r="AN1" s="83"/>
-      <c r="AO1" s="83"/>
-      <c r="AP1" s="83"/>
-      <c r="AQ1" s="83"/>
-      <c r="AR1" s="83"/>
-      <c r="AS1" s="83"/>
-      <c r="AT1" s="83"/>
-      <c r="AU1" s="84"/>
-      <c r="AV1" s="83"/>
-      <c r="AW1" s="83"/>
-      <c r="AX1" s="83"/>
-      <c r="AY1" s="83"/>
-      <c r="AZ1" s="83"/>
-      <c r="BA1" s="83"/>
-      <c r="BB1" s="83"/>
-      <c r="BC1" s="83"/>
-      <c r="BD1" s="83"/>
-      <c r="BE1" s="83"/>
-      <c r="BF1" s="83"/>
-      <c r="BG1" s="83"/>
-      <c r="BH1" s="83"/>
-      <c r="BI1" s="83"/>
-      <c r="BJ1" s="83"/>
-      <c r="BK1" s="83"/>
-      <c r="BL1" s="83"/>
-      <c r="BM1" s="83"/>
-      <c r="BN1" s="83"/>
-      <c r="BO1" s="83"/>
-      <c r="BP1" s="83"/>
-      <c r="BQ1" s="83"/>
-      <c r="BR1" s="83"/>
-      <c r="BS1" s="83"/>
-      <c r="BT1" s="83"/>
-      <c r="BU1" s="83"/>
-      <c r="BV1" s="85"/>
-      <c r="BW1" s="83"/>
-      <c r="BX1" s="83"/>
-      <c r="BY1" s="83"/>
-      <c r="BZ1" s="83"/>
-      <c r="CA1" s="83"/>
-      <c r="CB1" s="83"/>
-      <c r="CC1" s="83"/>
-      <c r="CD1" s="83"/>
-      <c r="CE1" s="83"/>
-      <c r="CF1" s="83"/>
-      <c r="CG1" s="83"/>
-      <c r="CH1" s="83"/>
-      <c r="CI1" s="83"/>
-      <c r="CJ1" s="83"/>
-      <c r="CK1" s="83"/>
-      <c r="CL1" s="83"/>
-      <c r="CM1" s="83"/>
-      <c r="CN1" s="83"/>
-      <c r="CO1" s="83"/>
-      <c r="CP1" s="83"/>
-      <c r="CQ1" s="83"/>
-      <c r="CR1" s="86"/>
-      <c r="CS1" s="89" t="s">
+      <c r="H1" s="96"/>
+      <c r="I1" s="96"/>
+      <c r="J1" s="96"/>
+      <c r="K1" s="96"/>
+      <c r="L1" s="96"/>
+      <c r="M1" s="96"/>
+      <c r="N1" s="96"/>
+      <c r="O1" s="96"/>
+      <c r="P1" s="149"/>
+      <c r="Q1" s="96"/>
+      <c r="R1" s="96"/>
+      <c r="S1" s="146"/>
+      <c r="T1" s="150"/>
+      <c r="U1" s="91"/>
+      <c r="V1" s="91"/>
+      <c r="W1" s="91"/>
+      <c r="X1" s="151"/>
+      <c r="Y1" s="91"/>
+      <c r="Z1" s="91"/>
+      <c r="AA1" s="91"/>
+      <c r="AB1" s="150"/>
+      <c r="AC1" s="91"/>
+      <c r="AD1" s="91"/>
+      <c r="AE1" s="91"/>
+      <c r="AF1" s="91"/>
+      <c r="AG1" s="91"/>
+      <c r="AH1" s="91"/>
+      <c r="AI1" s="91"/>
+      <c r="AJ1" s="91"/>
+      <c r="AK1" s="94"/>
+      <c r="AL1" s="90"/>
+      <c r="AM1" s="91"/>
+      <c r="AN1" s="91"/>
+      <c r="AO1" s="91"/>
+      <c r="AP1" s="91"/>
+      <c r="AQ1" s="91"/>
+      <c r="AR1" s="91"/>
+      <c r="AS1" s="91"/>
+      <c r="AT1" s="91"/>
+      <c r="AU1" s="92"/>
+      <c r="AV1" s="91"/>
+      <c r="AW1" s="91"/>
+      <c r="AX1" s="91"/>
+      <c r="AY1" s="91"/>
+      <c r="AZ1" s="91"/>
+      <c r="BA1" s="91"/>
+      <c r="BB1" s="91"/>
+      <c r="BC1" s="91"/>
+      <c r="BD1" s="91"/>
+      <c r="BE1" s="91"/>
+      <c r="BF1" s="91"/>
+      <c r="BG1" s="91"/>
+      <c r="BH1" s="91"/>
+      <c r="BI1" s="91"/>
+      <c r="BJ1" s="91"/>
+      <c r="BK1" s="91"/>
+      <c r="BL1" s="91"/>
+      <c r="BM1" s="91"/>
+      <c r="BN1" s="91"/>
+      <c r="BO1" s="91"/>
+      <c r="BP1" s="91"/>
+      <c r="BQ1" s="91"/>
+      <c r="BR1" s="91"/>
+      <c r="BS1" s="91"/>
+      <c r="BT1" s="91"/>
+      <c r="BU1" s="91"/>
+      <c r="BV1" s="93"/>
+      <c r="BW1" s="91"/>
+      <c r="BX1" s="91"/>
+      <c r="BY1" s="91"/>
+      <c r="BZ1" s="91"/>
+      <c r="CA1" s="91"/>
+      <c r="CB1" s="91"/>
+      <c r="CC1" s="91"/>
+      <c r="CD1" s="91"/>
+      <c r="CE1" s="91"/>
+      <c r="CF1" s="91"/>
+      <c r="CG1" s="91"/>
+      <c r="CH1" s="91"/>
+      <c r="CI1" s="91"/>
+      <c r="CJ1" s="91"/>
+      <c r="CK1" s="91"/>
+      <c r="CL1" s="91"/>
+      <c r="CM1" s="91"/>
+      <c r="CN1" s="91"/>
+      <c r="CO1" s="91"/>
+      <c r="CP1" s="91"/>
+      <c r="CQ1" s="91"/>
+      <c r="CR1" s="94"/>
+      <c r="CS1" s="97" t="s">
         <v>2</v>
       </c>
-      <c r="CT1" s="90"/>
-      <c r="CU1" s="90"/>
-      <c r="CV1" s="90"/>
-      <c r="CW1" s="91"/>
+      <c r="CT1" s="98"/>
+      <c r="CU1" s="98"/>
+      <c r="CV1" s="98"/>
+      <c r="CW1" s="99"/>
       <c r="CX1" s="1"/>
-      <c r="CY1" s="106" t="s">
+      <c r="CY1" s="114" t="s">
         <v>3</v>
       </c>
-      <c r="CZ1" s="93"/>
-      <c r="DA1" s="93"/>
-      <c r="DB1" s="93"/>
-      <c r="DC1" s="93"/>
-      <c r="DD1" s="93"/>
-      <c r="DE1" s="93"/>
-      <c r="DF1" s="93"/>
-      <c r="DG1" s="93"/>
+      <c r="CZ1" s="101"/>
+      <c r="DA1" s="101"/>
+      <c r="DB1" s="101"/>
+      <c r="DC1" s="101"/>
+      <c r="DD1" s="101"/>
+      <c r="DE1" s="101"/>
+      <c r="DF1" s="101"/>
+      <c r="DG1" s="101"/>
       <c r="DH1" s="1"/>
       <c r="DI1" s="1"/>
       <c r="DJ1" s="1"/>
@@ -4632,122 +4632,122 @@
       <c r="DW1" s="1"/>
     </row>
     <row r="2" spans="1:129" ht="16.5">
-      <c r="A2" s="156"/>
-      <c r="B2" s="157"/>
-      <c r="C2" s="156"/>
-      <c r="D2" s="136"/>
-      <c r="E2" s="136"/>
-      <c r="F2" s="157"/>
-      <c r="G2" s="134" t="s">
+      <c r="A2" s="164"/>
+      <c r="B2" s="165"/>
+      <c r="C2" s="164"/>
+      <c r="D2" s="144"/>
+      <c r="E2" s="144"/>
+      <c r="F2" s="165"/>
+      <c r="G2" s="142" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
-      <c r="K2" s="88"/>
-      <c r="L2" s="88"/>
-      <c r="M2" s="88"/>
-      <c r="N2" s="88"/>
-      <c r="O2" s="88"/>
-      <c r="P2" s="135"/>
-      <c r="Q2" s="136"/>
-      <c r="R2" s="136"/>
-      <c r="S2" s="136"/>
-      <c r="T2" s="98"/>
-      <c r="U2" s="88"/>
-      <c r="V2" s="88"/>
-      <c r="W2" s="100"/>
-      <c r="X2" s="102"/>
-      <c r="Y2" s="88"/>
-      <c r="Z2" s="88"/>
-      <c r="AA2" s="88"/>
-      <c r="AB2" s="144"/>
-      <c r="AC2" s="88"/>
-      <c r="AD2" s="88"/>
-      <c r="AE2" s="88"/>
-      <c r="AF2" s="88"/>
-      <c r="AG2" s="88"/>
-      <c r="AH2" s="88"/>
-      <c r="AI2" s="88"/>
-      <c r="AJ2" s="88"/>
-      <c r="AK2" s="100"/>
-      <c r="AL2" s="102"/>
-      <c r="AM2" s="88"/>
-      <c r="AN2" s="88"/>
-      <c r="AO2" s="88"/>
-      <c r="AP2" s="88"/>
-      <c r="AQ2" s="88"/>
-      <c r="AR2" s="88"/>
-      <c r="AS2" s="88"/>
-      <c r="AT2" s="88"/>
-      <c r="AU2" s="98"/>
-      <c r="AV2" s="88"/>
-      <c r="AW2" s="88"/>
-      <c r="AX2" s="88"/>
-      <c r="AY2" s="88"/>
-      <c r="AZ2" s="88"/>
-      <c r="BA2" s="88"/>
-      <c r="BB2" s="88"/>
-      <c r="BC2" s="88"/>
-      <c r="BD2" s="88"/>
-      <c r="BE2" s="88"/>
-      <c r="BF2" s="88"/>
-      <c r="BG2" s="88"/>
-      <c r="BH2" s="88"/>
-      <c r="BI2" s="88"/>
-      <c r="BJ2" s="88"/>
-      <c r="BK2" s="88"/>
-      <c r="BL2" s="88"/>
-      <c r="BM2" s="88"/>
-      <c r="BN2" s="88"/>
-      <c r="BO2" s="88"/>
-      <c r="BP2" s="88"/>
-      <c r="BQ2" s="88"/>
-      <c r="BR2" s="88"/>
-      <c r="BS2" s="88"/>
-      <c r="BT2" s="88"/>
-      <c r="BU2" s="88"/>
-      <c r="BV2" s="99"/>
-      <c r="BW2" s="88"/>
-      <c r="BX2" s="88"/>
-      <c r="BY2" s="88"/>
-      <c r="BZ2" s="88"/>
-      <c r="CA2" s="88"/>
-      <c r="CB2" s="88"/>
-      <c r="CC2" s="88"/>
-      <c r="CD2" s="88"/>
-      <c r="CE2" s="88"/>
-      <c r="CF2" s="88"/>
-      <c r="CG2" s="88"/>
-      <c r="CH2" s="88"/>
-      <c r="CI2" s="88"/>
-      <c r="CJ2" s="88"/>
-      <c r="CK2" s="88"/>
-      <c r="CL2" s="88"/>
-      <c r="CM2" s="88"/>
-      <c r="CN2" s="88"/>
-      <c r="CO2" s="88"/>
-      <c r="CP2" s="88"/>
-      <c r="CQ2" s="88"/>
-      <c r="CR2" s="100"/>
-      <c r="CS2" s="92"/>
-      <c r="CT2" s="93"/>
-      <c r="CU2" s="93"/>
-      <c r="CV2" s="93"/>
-      <c r="CW2" s="94"/>
+      <c r="H2" s="96"/>
+      <c r="I2" s="96"/>
+      <c r="J2" s="96"/>
+      <c r="K2" s="96"/>
+      <c r="L2" s="96"/>
+      <c r="M2" s="96"/>
+      <c r="N2" s="96"/>
+      <c r="O2" s="96"/>
+      <c r="P2" s="143"/>
+      <c r="Q2" s="144"/>
+      <c r="R2" s="144"/>
+      <c r="S2" s="144"/>
+      <c r="T2" s="106"/>
+      <c r="U2" s="96"/>
+      <c r="V2" s="96"/>
+      <c r="W2" s="108"/>
+      <c r="X2" s="110"/>
+      <c r="Y2" s="96"/>
+      <c r="Z2" s="96"/>
+      <c r="AA2" s="96"/>
+      <c r="AB2" s="152"/>
+      <c r="AC2" s="96"/>
+      <c r="AD2" s="96"/>
+      <c r="AE2" s="96"/>
+      <c r="AF2" s="96"/>
+      <c r="AG2" s="96"/>
+      <c r="AH2" s="96"/>
+      <c r="AI2" s="96"/>
+      <c r="AJ2" s="96"/>
+      <c r="AK2" s="108"/>
+      <c r="AL2" s="110"/>
+      <c r="AM2" s="96"/>
+      <c r="AN2" s="96"/>
+      <c r="AO2" s="96"/>
+      <c r="AP2" s="96"/>
+      <c r="AQ2" s="96"/>
+      <c r="AR2" s="96"/>
+      <c r="AS2" s="96"/>
+      <c r="AT2" s="96"/>
+      <c r="AU2" s="106"/>
+      <c r="AV2" s="96"/>
+      <c r="AW2" s="96"/>
+      <c r="AX2" s="96"/>
+      <c r="AY2" s="96"/>
+      <c r="AZ2" s="96"/>
+      <c r="BA2" s="96"/>
+      <c r="BB2" s="96"/>
+      <c r="BC2" s="96"/>
+      <c r="BD2" s="96"/>
+      <c r="BE2" s="96"/>
+      <c r="BF2" s="96"/>
+      <c r="BG2" s="96"/>
+      <c r="BH2" s="96"/>
+      <c r="BI2" s="96"/>
+      <c r="BJ2" s="96"/>
+      <c r="BK2" s="96"/>
+      <c r="BL2" s="96"/>
+      <c r="BM2" s="96"/>
+      <c r="BN2" s="96"/>
+      <c r="BO2" s="96"/>
+      <c r="BP2" s="96"/>
+      <c r="BQ2" s="96"/>
+      <c r="BR2" s="96"/>
+      <c r="BS2" s="96"/>
+      <c r="BT2" s="96"/>
+      <c r="BU2" s="96"/>
+      <c r="BV2" s="107"/>
+      <c r="BW2" s="96"/>
+      <c r="BX2" s="96"/>
+      <c r="BY2" s="96"/>
+      <c r="BZ2" s="96"/>
+      <c r="CA2" s="96"/>
+      <c r="CB2" s="96"/>
+      <c r="CC2" s="96"/>
+      <c r="CD2" s="96"/>
+      <c r="CE2" s="96"/>
+      <c r="CF2" s="96"/>
+      <c r="CG2" s="96"/>
+      <c r="CH2" s="96"/>
+      <c r="CI2" s="96"/>
+      <c r="CJ2" s="96"/>
+      <c r="CK2" s="96"/>
+      <c r="CL2" s="96"/>
+      <c r="CM2" s="96"/>
+      <c r="CN2" s="96"/>
+      <c r="CO2" s="96"/>
+      <c r="CP2" s="96"/>
+      <c r="CQ2" s="96"/>
+      <c r="CR2" s="108"/>
+      <c r="CS2" s="100"/>
+      <c r="CT2" s="101"/>
+      <c r="CU2" s="101"/>
+      <c r="CV2" s="101"/>
+      <c r="CW2" s="102"/>
       <c r="CX2" s="1"/>
-      <c r="CY2" s="107">
+      <c r="CY2" s="115">
         <f>COUNTA('BASE DE DATOS'!B10:B49)</f>
         <v>38</v>
       </c>
-      <c r="CZ2" s="108"/>
-      <c r="DA2" s="108"/>
-      <c r="DB2" s="108"/>
-      <c r="DC2" s="108"/>
-      <c r="DD2" s="108"/>
-      <c r="DE2" s="108"/>
-      <c r="DF2" s="108"/>
-      <c r="DG2" s="108"/>
+      <c r="CZ2" s="116"/>
+      <c r="DA2" s="116"/>
+      <c r="DB2" s="116"/>
+      <c r="DC2" s="116"/>
+      <c r="DD2" s="116"/>
+      <c r="DE2" s="116"/>
+      <c r="DF2" s="116"/>
+      <c r="DG2" s="116"/>
       <c r="DH2" s="1"/>
       <c r="DI2" s="1"/>
       <c r="DJ2" s="1"/>
@@ -4766,113 +4766,113 @@
       <c r="DW2" s="1"/>
     </row>
     <row r="3" spans="1:129" ht="16.5">
-      <c r="A3" s="137" t="s">
+      <c r="A3" s="145" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="88"/>
-      <c r="C3" s="138"/>
-      <c r="D3" s="139" t="s">
+      <c r="B3" s="96"/>
+      <c r="C3" s="146"/>
+      <c r="D3" s="147" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="88"/>
-      <c r="F3" s="138"/>
-      <c r="G3" s="146" t="s">
+      <c r="E3" s="96"/>
+      <c r="F3" s="146"/>
+      <c r="G3" s="154" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
-      <c r="K3" s="88"/>
-      <c r="L3" s="88"/>
-      <c r="M3" s="88"/>
-      <c r="N3" s="88"/>
-      <c r="O3" s="88"/>
-      <c r="P3" s="140"/>
-      <c r="Q3" s="88"/>
-      <c r="R3" s="88"/>
-      <c r="S3" s="88"/>
-      <c r="T3" s="129"/>
-      <c r="U3" s="88"/>
-      <c r="V3" s="88"/>
-      <c r="W3" s="100"/>
-      <c r="X3" s="130"/>
-      <c r="Y3" s="88"/>
-      <c r="Z3" s="88"/>
-      <c r="AA3" s="88"/>
-      <c r="AB3" s="129"/>
-      <c r="AC3" s="88"/>
-      <c r="AD3" s="88"/>
-      <c r="AE3" s="88"/>
-      <c r="AF3" s="88"/>
-      <c r="AG3" s="88"/>
-      <c r="AH3" s="88"/>
-      <c r="AI3" s="88"/>
-      <c r="AJ3" s="88"/>
-      <c r="AK3" s="100"/>
-      <c r="AL3" s="87"/>
-      <c r="AM3" s="88"/>
-      <c r="AN3" s="88"/>
-      <c r="AO3" s="88"/>
-      <c r="AP3" s="88"/>
-      <c r="AQ3" s="88"/>
-      <c r="AR3" s="88"/>
-      <c r="AS3" s="88"/>
-      <c r="AT3" s="88"/>
-      <c r="AU3" s="113"/>
-      <c r="AV3" s="88"/>
-      <c r="AW3" s="88"/>
-      <c r="AX3" s="88"/>
-      <c r="AY3" s="88"/>
-      <c r="AZ3" s="88"/>
-      <c r="BA3" s="88"/>
-      <c r="BB3" s="88"/>
-      <c r="BC3" s="88"/>
-      <c r="BD3" s="88"/>
-      <c r="BE3" s="88"/>
-      <c r="BF3" s="88"/>
-      <c r="BG3" s="88"/>
-      <c r="BH3" s="88"/>
-      <c r="BI3" s="88"/>
-      <c r="BJ3" s="88"/>
-      <c r="BK3" s="88"/>
-      <c r="BL3" s="88"/>
-      <c r="BM3" s="88"/>
-      <c r="BN3" s="88"/>
-      <c r="BO3" s="88"/>
-      <c r="BP3" s="88"/>
-      <c r="BQ3" s="88"/>
-      <c r="BR3" s="88"/>
-      <c r="BS3" s="88"/>
-      <c r="BT3" s="88"/>
-      <c r="BU3" s="88"/>
-      <c r="BV3" s="101"/>
-      <c r="BW3" s="88"/>
-      <c r="BX3" s="88"/>
-      <c r="BY3" s="88"/>
-      <c r="BZ3" s="88"/>
-      <c r="CA3" s="88"/>
-      <c r="CB3" s="88"/>
-      <c r="CC3" s="88"/>
-      <c r="CD3" s="88"/>
-      <c r="CE3" s="88"/>
-      <c r="CF3" s="88"/>
-      <c r="CG3" s="88"/>
-      <c r="CH3" s="88"/>
-      <c r="CI3" s="88"/>
-      <c r="CJ3" s="88"/>
-      <c r="CK3" s="88"/>
-      <c r="CL3" s="88"/>
-      <c r="CM3" s="88"/>
-      <c r="CN3" s="88"/>
-      <c r="CO3" s="88"/>
-      <c r="CP3" s="88"/>
-      <c r="CQ3" s="88"/>
-      <c r="CR3" s="100"/>
-      <c r="CS3" s="92"/>
-      <c r="CT3" s="93"/>
-      <c r="CU3" s="93"/>
-      <c r="CV3" s="93"/>
-      <c r="CW3" s="94"/>
+      <c r="H3" s="96"/>
+      <c r="I3" s="96"/>
+      <c r="J3" s="96"/>
+      <c r="K3" s="96"/>
+      <c r="L3" s="96"/>
+      <c r="M3" s="96"/>
+      <c r="N3" s="96"/>
+      <c r="O3" s="96"/>
+      <c r="P3" s="148"/>
+      <c r="Q3" s="96"/>
+      <c r="R3" s="96"/>
+      <c r="S3" s="96"/>
+      <c r="T3" s="137"/>
+      <c r="U3" s="96"/>
+      <c r="V3" s="96"/>
+      <c r="W3" s="108"/>
+      <c r="X3" s="138"/>
+      <c r="Y3" s="96"/>
+      <c r="Z3" s="96"/>
+      <c r="AA3" s="96"/>
+      <c r="AB3" s="137"/>
+      <c r="AC3" s="96"/>
+      <c r="AD3" s="96"/>
+      <c r="AE3" s="96"/>
+      <c r="AF3" s="96"/>
+      <c r="AG3" s="96"/>
+      <c r="AH3" s="96"/>
+      <c r="AI3" s="96"/>
+      <c r="AJ3" s="96"/>
+      <c r="AK3" s="108"/>
+      <c r="AL3" s="95"/>
+      <c r="AM3" s="96"/>
+      <c r="AN3" s="96"/>
+      <c r="AO3" s="96"/>
+      <c r="AP3" s="96"/>
+      <c r="AQ3" s="96"/>
+      <c r="AR3" s="96"/>
+      <c r="AS3" s="96"/>
+      <c r="AT3" s="96"/>
+      <c r="AU3" s="121"/>
+      <c r="AV3" s="96"/>
+      <c r="AW3" s="96"/>
+      <c r="AX3" s="96"/>
+      <c r="AY3" s="96"/>
+      <c r="AZ3" s="96"/>
+      <c r="BA3" s="96"/>
+      <c r="BB3" s="96"/>
+      <c r="BC3" s="96"/>
+      <c r="BD3" s="96"/>
+      <c r="BE3" s="96"/>
+      <c r="BF3" s="96"/>
+      <c r="BG3" s="96"/>
+      <c r="BH3" s="96"/>
+      <c r="BI3" s="96"/>
+      <c r="BJ3" s="96"/>
+      <c r="BK3" s="96"/>
+      <c r="BL3" s="96"/>
+      <c r="BM3" s="96"/>
+      <c r="BN3" s="96"/>
+      <c r="BO3" s="96"/>
+      <c r="BP3" s="96"/>
+      <c r="BQ3" s="96"/>
+      <c r="BR3" s="96"/>
+      <c r="BS3" s="96"/>
+      <c r="BT3" s="96"/>
+      <c r="BU3" s="96"/>
+      <c r="BV3" s="109"/>
+      <c r="BW3" s="96"/>
+      <c r="BX3" s="96"/>
+      <c r="BY3" s="96"/>
+      <c r="BZ3" s="96"/>
+      <c r="CA3" s="96"/>
+      <c r="CB3" s="96"/>
+      <c r="CC3" s="96"/>
+      <c r="CD3" s="96"/>
+      <c r="CE3" s="96"/>
+      <c r="CF3" s="96"/>
+      <c r="CG3" s="96"/>
+      <c r="CH3" s="96"/>
+      <c r="CI3" s="96"/>
+      <c r="CJ3" s="96"/>
+      <c r="CK3" s="96"/>
+      <c r="CL3" s="96"/>
+      <c r="CM3" s="96"/>
+      <c r="CN3" s="96"/>
+      <c r="CO3" s="96"/>
+      <c r="CP3" s="96"/>
+      <c r="CQ3" s="96"/>
+      <c r="CR3" s="108"/>
+      <c r="CS3" s="100"/>
+      <c r="CT3" s="101"/>
+      <c r="CU3" s="101"/>
+      <c r="CV3" s="101"/>
+      <c r="CW3" s="102"/>
       <c r="CX3" s="1"/>
       <c r="CY3" s="1"/>
       <c r="CZ3" s="1"/>
@@ -4901,142 +4901,142 @@
       <c r="DW3" s="1"/>
     </row>
     <row r="4" spans="1:129" ht="15.75">
-      <c r="A4" s="137" t="s">
+      <c r="A4" s="145" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="88"/>
-      <c r="C4" s="138"/>
-      <c r="D4" s="145" t="s">
+      <c r="B4" s="96"/>
+      <c r="C4" s="146"/>
+      <c r="D4" s="153" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="88"/>
-      <c r="F4" s="138"/>
-      <c r="G4" s="147" t="s">
+      <c r="E4" s="96"/>
+      <c r="F4" s="146"/>
+      <c r="G4" s="155" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="104"/>
-      <c r="I4" s="104"/>
-      <c r="J4" s="104"/>
-      <c r="K4" s="104"/>
-      <c r="L4" s="104"/>
-      <c r="M4" s="104"/>
-      <c r="N4" s="104"/>
-      <c r="O4" s="104"/>
-      <c r="P4" s="149"/>
-      <c r="Q4" s="104"/>
-      <c r="R4" s="104"/>
-      <c r="S4" s="104"/>
-      <c r="T4" s="150"/>
-      <c r="U4" s="104"/>
-      <c r="V4" s="104"/>
-      <c r="W4" s="105"/>
-      <c r="X4" s="151"/>
-      <c r="Y4" s="104"/>
-      <c r="Z4" s="104"/>
-      <c r="AA4" s="104"/>
-      <c r="AB4" s="152"/>
-      <c r="AC4" s="104"/>
-      <c r="AD4" s="104"/>
-      <c r="AE4" s="104"/>
-      <c r="AF4" s="104"/>
-      <c r="AG4" s="104"/>
-      <c r="AH4" s="104"/>
-      <c r="AI4" s="104"/>
-      <c r="AJ4" s="104"/>
-      <c r="AK4" s="105"/>
-      <c r="AL4" s="103"/>
-      <c r="AM4" s="104"/>
-      <c r="AN4" s="104"/>
-      <c r="AO4" s="104"/>
-      <c r="AP4" s="104"/>
-      <c r="AQ4" s="104"/>
-      <c r="AR4" s="104"/>
-      <c r="AS4" s="104"/>
-      <c r="AT4" s="105"/>
-      <c r="AU4" s="114"/>
-      <c r="AV4" s="104"/>
-      <c r="AW4" s="104"/>
-      <c r="AX4" s="104"/>
-      <c r="AY4" s="104"/>
-      <c r="AZ4" s="104"/>
-      <c r="BA4" s="104"/>
-      <c r="BB4" s="104"/>
-      <c r="BC4" s="104"/>
-      <c r="BD4" s="104"/>
-      <c r="BE4" s="104"/>
-      <c r="BF4" s="104"/>
-      <c r="BG4" s="104"/>
-      <c r="BH4" s="104"/>
-      <c r="BI4" s="104"/>
-      <c r="BJ4" s="104"/>
-      <c r="BK4" s="104"/>
-      <c r="BL4" s="104"/>
-      <c r="BM4" s="104"/>
-      <c r="BN4" s="104"/>
-      <c r="BO4" s="104"/>
-      <c r="BP4" s="104"/>
-      <c r="BQ4" s="104"/>
-      <c r="BR4" s="104"/>
-      <c r="BS4" s="104"/>
-      <c r="BT4" s="104"/>
-      <c r="BU4" s="104"/>
-      <c r="BV4" s="115"/>
-      <c r="BW4" s="104"/>
-      <c r="BX4" s="104"/>
-      <c r="BY4" s="104"/>
-      <c r="BZ4" s="104"/>
-      <c r="CA4" s="104"/>
-      <c r="CB4" s="104"/>
-      <c r="CC4" s="104"/>
-      <c r="CD4" s="104"/>
-      <c r="CE4" s="104"/>
-      <c r="CF4" s="104"/>
-      <c r="CG4" s="104"/>
-      <c r="CH4" s="104"/>
-      <c r="CI4" s="104"/>
-      <c r="CJ4" s="104"/>
-      <c r="CK4" s="104"/>
-      <c r="CL4" s="104"/>
-      <c r="CM4" s="104"/>
-      <c r="CN4" s="104"/>
-      <c r="CO4" s="104"/>
-      <c r="CP4" s="104"/>
-      <c r="CQ4" s="104"/>
-      <c r="CR4" s="105"/>
-      <c r="CS4" s="92"/>
-      <c r="CT4" s="93"/>
-      <c r="CU4" s="93"/>
-      <c r="CV4" s="93"/>
-      <c r="CW4" s="94"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="112"/>
+      <c r="K4" s="112"/>
+      <c r="L4" s="112"/>
+      <c r="M4" s="112"/>
+      <c r="N4" s="112"/>
+      <c r="O4" s="112"/>
+      <c r="P4" s="157"/>
+      <c r="Q4" s="112"/>
+      <c r="R4" s="112"/>
+      <c r="S4" s="112"/>
+      <c r="T4" s="158"/>
+      <c r="U4" s="112"/>
+      <c r="V4" s="112"/>
+      <c r="W4" s="113"/>
+      <c r="X4" s="159"/>
+      <c r="Y4" s="112"/>
+      <c r="Z4" s="112"/>
+      <c r="AA4" s="112"/>
+      <c r="AB4" s="160"/>
+      <c r="AC4" s="112"/>
+      <c r="AD4" s="112"/>
+      <c r="AE4" s="112"/>
+      <c r="AF4" s="112"/>
+      <c r="AG4" s="112"/>
+      <c r="AH4" s="112"/>
+      <c r="AI4" s="112"/>
+      <c r="AJ4" s="112"/>
+      <c r="AK4" s="113"/>
+      <c r="AL4" s="111"/>
+      <c r="AM4" s="112"/>
+      <c r="AN4" s="112"/>
+      <c r="AO4" s="112"/>
+      <c r="AP4" s="112"/>
+      <c r="AQ4" s="112"/>
+      <c r="AR4" s="112"/>
+      <c r="AS4" s="112"/>
+      <c r="AT4" s="113"/>
+      <c r="AU4" s="122"/>
+      <c r="AV4" s="112"/>
+      <c r="AW4" s="112"/>
+      <c r="AX4" s="112"/>
+      <c r="AY4" s="112"/>
+      <c r="AZ4" s="112"/>
+      <c r="BA4" s="112"/>
+      <c r="BB4" s="112"/>
+      <c r="BC4" s="112"/>
+      <c r="BD4" s="112"/>
+      <c r="BE4" s="112"/>
+      <c r="BF4" s="112"/>
+      <c r="BG4" s="112"/>
+      <c r="BH4" s="112"/>
+      <c r="BI4" s="112"/>
+      <c r="BJ4" s="112"/>
+      <c r="BK4" s="112"/>
+      <c r="BL4" s="112"/>
+      <c r="BM4" s="112"/>
+      <c r="BN4" s="112"/>
+      <c r="BO4" s="112"/>
+      <c r="BP4" s="112"/>
+      <c r="BQ4" s="112"/>
+      <c r="BR4" s="112"/>
+      <c r="BS4" s="112"/>
+      <c r="BT4" s="112"/>
+      <c r="BU4" s="112"/>
+      <c r="BV4" s="123"/>
+      <c r="BW4" s="112"/>
+      <c r="BX4" s="112"/>
+      <c r="BY4" s="112"/>
+      <c r="BZ4" s="112"/>
+      <c r="CA4" s="112"/>
+      <c r="CB4" s="112"/>
+      <c r="CC4" s="112"/>
+      <c r="CD4" s="112"/>
+      <c r="CE4" s="112"/>
+      <c r="CF4" s="112"/>
+      <c r="CG4" s="112"/>
+      <c r="CH4" s="112"/>
+      <c r="CI4" s="112"/>
+      <c r="CJ4" s="112"/>
+      <c r="CK4" s="112"/>
+      <c r="CL4" s="112"/>
+      <c r="CM4" s="112"/>
+      <c r="CN4" s="112"/>
+      <c r="CO4" s="112"/>
+      <c r="CP4" s="112"/>
+      <c r="CQ4" s="112"/>
+      <c r="CR4" s="113"/>
+      <c r="CS4" s="100"/>
+      <c r="CT4" s="101"/>
+      <c r="CU4" s="101"/>
+      <c r="CV4" s="101"/>
+      <c r="CW4" s="102"/>
       <c r="CX4" s="1"/>
-      <c r="CY4" s="109" t="s">
+      <c r="CY4" s="117" t="s">
         <v>11</v>
       </c>
-      <c r="CZ4" s="110"/>
-      <c r="DA4" s="111" t="s">
+      <c r="CZ4" s="118"/>
+      <c r="DA4" s="119" t="s">
         <v>12</v>
       </c>
-      <c r="DB4" s="112"/>
-      <c r="DC4" s="112"/>
-      <c r="DD4" s="112"/>
-      <c r="DE4" s="112"/>
-      <c r="DF4" s="112"/>
-      <c r="DG4" s="110"/>
+      <c r="DB4" s="120"/>
+      <c r="DC4" s="120"/>
+      <c r="DD4" s="120"/>
+      <c r="DE4" s="120"/>
+      <c r="DF4" s="120"/>
+      <c r="DG4" s="118"/>
       <c r="DH4" s="1"/>
       <c r="DI4" s="1"/>
-      <c r="DJ4" s="109" t="s">
+      <c r="DJ4" s="117" t="s">
         <v>13</v>
       </c>
-      <c r="DK4" s="110"/>
-      <c r="DL4" s="111" t="s">
+      <c r="DK4" s="118"/>
+      <c r="DL4" s="119" t="s">
         <v>14</v>
       </c>
-      <c r="DM4" s="112"/>
-      <c r="DN4" s="112"/>
-      <c r="DO4" s="112"/>
-      <c r="DP4" s="112"/>
-      <c r="DQ4" s="112"/>
-      <c r="DR4" s="110"/>
+      <c r="DM4" s="120"/>
+      <c r="DN4" s="120"/>
+      <c r="DO4" s="120"/>
+      <c r="DP4" s="120"/>
+      <c r="DQ4" s="120"/>
+      <c r="DR4" s="118"/>
       <c r="DS4" s="1"/>
       <c r="DT4" s="1"/>
       <c r="DU4" s="1"/>
@@ -5044,112 +5044,112 @@
       <c r="DW4" s="1"/>
     </row>
     <row r="5" spans="1:129" ht="15.75">
-      <c r="A5" s="137" t="s">
+      <c r="A5" s="145" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="88"/>
-      <c r="C5" s="138"/>
-      <c r="D5" s="153" t="str">
+      <c r="B5" s="96"/>
+      <c r="C5" s="146"/>
+      <c r="D5" s="161" t="str">
         <f>'BASE DE DATOS'!C7</f>
         <v>COLEGIO TOMAS CIPRIANO DE MOSQUERA (IED)</v>
       </c>
-      <c r="E5" s="88"/>
-      <c r="F5" s="138"/>
-      <c r="G5" s="148"/>
-      <c r="H5" s="108"/>
-      <c r="I5" s="108"/>
-      <c r="J5" s="108"/>
-      <c r="K5" s="108"/>
-      <c r="L5" s="108"/>
-      <c r="M5" s="108"/>
-      <c r="N5" s="108"/>
-      <c r="O5" s="108"/>
-      <c r="P5" s="95"/>
-      <c r="Q5" s="96"/>
-      <c r="R5" s="96"/>
-      <c r="S5" s="96"/>
-      <c r="T5" s="95"/>
-      <c r="U5" s="96"/>
-      <c r="V5" s="96"/>
-      <c r="W5" s="97"/>
-      <c r="X5" s="95"/>
-      <c r="Y5" s="96"/>
-      <c r="Z5" s="96"/>
-      <c r="AA5" s="96"/>
-      <c r="AB5" s="95"/>
-      <c r="AC5" s="96"/>
-      <c r="AD5" s="96"/>
-      <c r="AE5" s="96"/>
-      <c r="AF5" s="96"/>
-      <c r="AG5" s="96"/>
-      <c r="AH5" s="96"/>
-      <c r="AI5" s="96"/>
-      <c r="AJ5" s="96"/>
-      <c r="AK5" s="97"/>
-      <c r="AL5" s="95"/>
-      <c r="AM5" s="96"/>
-      <c r="AN5" s="96"/>
-      <c r="AO5" s="96"/>
-      <c r="AP5" s="96"/>
-      <c r="AQ5" s="96"/>
-      <c r="AR5" s="96"/>
-      <c r="AS5" s="96"/>
-      <c r="AT5" s="97"/>
-      <c r="AU5" s="95"/>
-      <c r="AV5" s="96"/>
-      <c r="AW5" s="96"/>
-      <c r="AX5" s="96"/>
-      <c r="AY5" s="96"/>
-      <c r="AZ5" s="96"/>
-      <c r="BA5" s="96"/>
-      <c r="BB5" s="96"/>
-      <c r="BC5" s="96"/>
-      <c r="BD5" s="96"/>
-      <c r="BE5" s="96"/>
-      <c r="BF5" s="96"/>
-      <c r="BG5" s="96"/>
-      <c r="BH5" s="96"/>
-      <c r="BI5" s="96"/>
-      <c r="BJ5" s="96"/>
-      <c r="BK5" s="96"/>
-      <c r="BL5" s="96"/>
-      <c r="BM5" s="96"/>
-      <c r="BN5" s="96"/>
-      <c r="BO5" s="96"/>
-      <c r="BP5" s="96"/>
-      <c r="BQ5" s="96"/>
-      <c r="BR5" s="96"/>
-      <c r="BS5" s="96"/>
-      <c r="BT5" s="96"/>
-      <c r="BU5" s="96"/>
-      <c r="BV5" s="95"/>
-      <c r="BW5" s="96"/>
-      <c r="BX5" s="96"/>
-      <c r="BY5" s="96"/>
-      <c r="BZ5" s="96"/>
-      <c r="CA5" s="96"/>
-      <c r="CB5" s="96"/>
-      <c r="CC5" s="96"/>
-      <c r="CD5" s="96"/>
-      <c r="CE5" s="96"/>
-      <c r="CF5" s="96"/>
-      <c r="CG5" s="96"/>
-      <c r="CH5" s="96"/>
-      <c r="CI5" s="96"/>
-      <c r="CJ5" s="96"/>
-      <c r="CK5" s="96"/>
-      <c r="CL5" s="96"/>
-      <c r="CM5" s="96"/>
-      <c r="CN5" s="96"/>
-      <c r="CO5" s="96"/>
-      <c r="CP5" s="96"/>
-      <c r="CQ5" s="96"/>
-      <c r="CR5" s="97"/>
-      <c r="CS5" s="95"/>
-      <c r="CT5" s="96"/>
-      <c r="CU5" s="96"/>
-      <c r="CV5" s="96"/>
-      <c r="CW5" s="97"/>
+      <c r="E5" s="96"/>
+      <c r="F5" s="146"/>
+      <c r="G5" s="156"/>
+      <c r="H5" s="116"/>
+      <c r="I5" s="116"/>
+      <c r="J5" s="116"/>
+      <c r="K5" s="116"/>
+      <c r="L5" s="116"/>
+      <c r="M5" s="116"/>
+      <c r="N5" s="116"/>
+      <c r="O5" s="116"/>
+      <c r="P5" s="103"/>
+      <c r="Q5" s="104"/>
+      <c r="R5" s="104"/>
+      <c r="S5" s="104"/>
+      <c r="T5" s="103"/>
+      <c r="U5" s="104"/>
+      <c r="V5" s="104"/>
+      <c r="W5" s="105"/>
+      <c r="X5" s="103"/>
+      <c r="Y5" s="104"/>
+      <c r="Z5" s="104"/>
+      <c r="AA5" s="104"/>
+      <c r="AB5" s="103"/>
+      <c r="AC5" s="104"/>
+      <c r="AD5" s="104"/>
+      <c r="AE5" s="104"/>
+      <c r="AF5" s="104"/>
+      <c r="AG5" s="104"/>
+      <c r="AH5" s="104"/>
+      <c r="AI5" s="104"/>
+      <c r="AJ5" s="104"/>
+      <c r="AK5" s="105"/>
+      <c r="AL5" s="103"/>
+      <c r="AM5" s="104"/>
+      <c r="AN5" s="104"/>
+      <c r="AO5" s="104"/>
+      <c r="AP5" s="104"/>
+      <c r="AQ5" s="104"/>
+      <c r="AR5" s="104"/>
+      <c r="AS5" s="104"/>
+      <c r="AT5" s="105"/>
+      <c r="AU5" s="103"/>
+      <c r="AV5" s="104"/>
+      <c r="AW5" s="104"/>
+      <c r="AX5" s="104"/>
+      <c r="AY5" s="104"/>
+      <c r="AZ5" s="104"/>
+      <c r="BA5" s="104"/>
+      <c r="BB5" s="104"/>
+      <c r="BC5" s="104"/>
+      <c r="BD5" s="104"/>
+      <c r="BE5" s="104"/>
+      <c r="BF5" s="104"/>
+      <c r="BG5" s="104"/>
+      <c r="BH5" s="104"/>
+      <c r="BI5" s="104"/>
+      <c r="BJ5" s="104"/>
+      <c r="BK5" s="104"/>
+      <c r="BL5" s="104"/>
+      <c r="BM5" s="104"/>
+      <c r="BN5" s="104"/>
+      <c r="BO5" s="104"/>
+      <c r="BP5" s="104"/>
+      <c r="BQ5" s="104"/>
+      <c r="BR5" s="104"/>
+      <c r="BS5" s="104"/>
+      <c r="BT5" s="104"/>
+      <c r="BU5" s="104"/>
+      <c r="BV5" s="103"/>
+      <c r="BW5" s="104"/>
+      <c r="BX5" s="104"/>
+      <c r="BY5" s="104"/>
+      <c r="BZ5" s="104"/>
+      <c r="CA5" s="104"/>
+      <c r="CB5" s="104"/>
+      <c r="CC5" s="104"/>
+      <c r="CD5" s="104"/>
+      <c r="CE5" s="104"/>
+      <c r="CF5" s="104"/>
+      <c r="CG5" s="104"/>
+      <c r="CH5" s="104"/>
+      <c r="CI5" s="104"/>
+      <c r="CJ5" s="104"/>
+      <c r="CK5" s="104"/>
+      <c r="CL5" s="104"/>
+      <c r="CM5" s="104"/>
+      <c r="CN5" s="104"/>
+      <c r="CO5" s="104"/>
+      <c r="CP5" s="104"/>
+      <c r="CQ5" s="104"/>
+      <c r="CR5" s="105"/>
+      <c r="CS5" s="103"/>
+      <c r="CT5" s="104"/>
+      <c r="CU5" s="104"/>
+      <c r="CV5" s="104"/>
+      <c r="CW5" s="105"/>
       <c r="CX5" s="1"/>
       <c r="CY5" s="1"/>
       <c r="CZ5" s="1"/>
@@ -5178,11 +5178,11 @@
       <c r="DW5" s="1"/>
     </row>
     <row r="6" spans="1:129" ht="15.75">
-      <c r="A6" s="137" t="s">
+      <c r="A6" s="145" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="88"/>
-      <c r="C6" s="138"/>
+      <c r="B6" s="96"/>
+      <c r="C6" s="146"/>
       <c r="D6" s="3">
         <f>'BASE DE DATOS'!C4</f>
         <v>3458742</v>
@@ -5194,18 +5194,18 @@
         <f>'BASE DE DATOS'!G7</f>
         <v>10</v>
       </c>
-      <c r="G6" s="159" t="str">
+      <c r="G6" s="167" t="str">
         <f>CY1 &amp; " " &amp; CY2</f>
         <v>TOTAL APRENDICES MATRICULADOS: 38</v>
       </c>
-      <c r="H6" s="104"/>
-      <c r="I6" s="104"/>
-      <c r="J6" s="104"/>
-      <c r="K6" s="104"/>
-      <c r="L6" s="104"/>
-      <c r="M6" s="104"/>
-      <c r="N6" s="104"/>
-      <c r="O6" s="155"/>
+      <c r="H6" s="112"/>
+      <c r="I6" s="112"/>
+      <c r="J6" s="112"/>
+      <c r="K6" s="112"/>
+      <c r="L6" s="112"/>
+      <c r="M6" s="112"/>
+      <c r="N6" s="112"/>
+      <c r="O6" s="163"/>
       <c r="P6" s="6" t="str">
         <f t="shared" ref="P6:CW6" si="0">TEXT(P7,"MMM")</f>
         <v>mar</v>
@@ -5550,41 +5550,41 @@
         <f t="shared" si="0"/>
         <v>ene</v>
       </c>
-      <c r="CX6" s="116" t="s">
+      <c r="CX6" s="124" t="s">
         <v>18</v>
       </c>
-      <c r="CY6" s="117"/>
-      <c r="CZ6" s="117"/>
-      <c r="DA6" s="117"/>
-      <c r="DB6" s="117"/>
-      <c r="DC6" s="117"/>
-      <c r="DD6" s="117"/>
-      <c r="DE6" s="117"/>
-      <c r="DF6" s="117"/>
-      <c r="DG6" s="117"/>
-      <c r="DH6" s="117"/>
-      <c r="DI6" s="117"/>
-      <c r="DJ6" s="117"/>
-      <c r="DK6" s="117"/>
-      <c r="DL6" s="117"/>
-      <c r="DM6" s="117"/>
-      <c r="DN6" s="117"/>
-      <c r="DO6" s="117"/>
-      <c r="DP6" s="117"/>
-      <c r="DQ6" s="117"/>
-      <c r="DR6" s="117"/>
-      <c r="DS6" s="117"/>
-      <c r="DT6" s="117"/>
-      <c r="DU6" s="117"/>
-      <c r="DV6" s="117"/>
-      <c r="DW6" s="117"/>
+      <c r="CY6" s="125"/>
+      <c r="CZ6" s="125"/>
+      <c r="DA6" s="125"/>
+      <c r="DB6" s="125"/>
+      <c r="DC6" s="125"/>
+      <c r="DD6" s="125"/>
+      <c r="DE6" s="125"/>
+      <c r="DF6" s="125"/>
+      <c r="DG6" s="125"/>
+      <c r="DH6" s="125"/>
+      <c r="DI6" s="125"/>
+      <c r="DJ6" s="125"/>
+      <c r="DK6" s="125"/>
+      <c r="DL6" s="125"/>
+      <c r="DM6" s="125"/>
+      <c r="DN6" s="125"/>
+      <c r="DO6" s="125"/>
+      <c r="DP6" s="125"/>
+      <c r="DQ6" s="125"/>
+      <c r="DR6" s="125"/>
+      <c r="DS6" s="125"/>
+      <c r="DT6" s="125"/>
+      <c r="DU6" s="125"/>
+      <c r="DV6" s="125"/>
+      <c r="DW6" s="125"/>
     </row>
     <row r="7" spans="1:129" ht="22.5">
-      <c r="A7" s="160" t="s">
+      <c r="A7" s="168" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="88"/>
-      <c r="C7" s="138"/>
+      <c r="B7" s="96"/>
+      <c r="C7" s="146"/>
       <c r="D7" s="8">
         <f>'BASE DE DATOS'!G5</f>
         <v>46101</v>
@@ -5596,15 +5596,15 @@
         <f>'BASE DE DATOS'!G6</f>
         <v>46102</v>
       </c>
-      <c r="G7" s="156"/>
-      <c r="H7" s="136"/>
-      <c r="I7" s="136"/>
-      <c r="J7" s="136"/>
-      <c r="K7" s="136"/>
-      <c r="L7" s="136"/>
-      <c r="M7" s="136"/>
-      <c r="N7" s="136"/>
-      <c r="O7" s="157"/>
+      <c r="G7" s="164"/>
+      <c r="H7" s="144"/>
+      <c r="I7" s="144"/>
+      <c r="J7" s="144"/>
+      <c r="K7" s="144"/>
+      <c r="L7" s="144"/>
+      <c r="M7" s="144"/>
+      <c r="N7" s="144"/>
+      <c r="O7" s="165"/>
       <c r="P7" s="11">
         <f>D7</f>
         <v>46101</v>
@@ -5949,58 +5949,58 @@
         <f>IF('BASE DE DATOS'!$G$4=1,(CV7+7),IF('BASE DE DATOS'!$G$4=2,(CU7+7)))</f>
         <v>46396</v>
       </c>
-      <c r="CX7" s="118" t="s">
+      <c r="CX7" s="126" t="s">
         <v>21</v>
       </c>
-      <c r="CY7" s="119"/>
-      <c r="CZ7" s="118" t="s">
+      <c r="CY7" s="127"/>
+      <c r="CZ7" s="126" t="s">
         <v>22</v>
       </c>
-      <c r="DA7" s="117"/>
-      <c r="DB7" s="118" t="s">
+      <c r="DA7" s="125"/>
+      <c r="DB7" s="126" t="s">
         <v>23</v>
       </c>
-      <c r="DC7" s="119"/>
-      <c r="DD7" s="118" t="s">
+      <c r="DC7" s="127"/>
+      <c r="DD7" s="126" t="s">
         <v>24</v>
       </c>
-      <c r="DE7" s="119"/>
-      <c r="DF7" s="118" t="s">
+      <c r="DE7" s="127"/>
+      <c r="DF7" s="126" t="s">
         <v>25</v>
       </c>
-      <c r="DG7" s="119"/>
-      <c r="DH7" s="118" t="s">
+      <c r="DG7" s="127"/>
+      <c r="DH7" s="126" t="s">
         <v>26</v>
       </c>
-      <c r="DI7" s="119"/>
-      <c r="DJ7" s="118" t="s">
+      <c r="DI7" s="127"/>
+      <c r="DJ7" s="126" t="s">
         <v>27</v>
       </c>
-      <c r="DK7" s="119"/>
-      <c r="DL7" s="118" t="s">
+      <c r="DK7" s="127"/>
+      <c r="DL7" s="126" t="s">
         <v>28</v>
       </c>
-      <c r="DM7" s="119"/>
-      <c r="DN7" s="118" t="s">
+      <c r="DM7" s="127"/>
+      <c r="DN7" s="126" t="s">
         <v>29</v>
       </c>
-      <c r="DO7" s="119"/>
-      <c r="DP7" s="118" t="s">
+      <c r="DO7" s="127"/>
+      <c r="DP7" s="126" t="s">
         <v>30</v>
       </c>
-      <c r="DQ7" s="119"/>
-      <c r="DR7" s="118" t="s">
+      <c r="DQ7" s="127"/>
+      <c r="DR7" s="126" t="s">
         <v>31</v>
       </c>
-      <c r="DS7" s="119"/>
-      <c r="DT7" s="118" t="s">
+      <c r="DS7" s="127"/>
+      <c r="DT7" s="126" t="s">
         <v>32</v>
       </c>
-      <c r="DU7" s="119"/>
-      <c r="DV7" s="120" t="s">
+      <c r="DU7" s="127"/>
+      <c r="DV7" s="128" t="s">
         <v>33</v>
       </c>
-      <c r="DW7" s="117"/>
+      <c r="DW7" s="125"/>
     </row>
     <row r="8" spans="1:129" ht="30.75" customHeight="1">
       <c r="A8" s="13" t="s">
@@ -6499,7 +6499,7 @@
       </c>
       <c r="G9" s="31">
         <f t="shared" ref="G9:G37" si="3">COUNTIF(P9:CR9,"A")</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H9" s="32">
         <f t="shared" ref="H9:H37" si="4">COUNTIF(P9:CR9,"CE")</f>
@@ -6539,12 +6539,18 @@
       <c r="Q9" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="R9" s="35"/>
+      <c r="R9" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="S9" s="35"/>
       <c r="T9" s="35"/>
       <c r="U9" s="35"/>
-      <c r="V9" s="35"/>
-      <c r="W9" s="35"/>
+      <c r="V9" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="W9" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X9" s="35"/>
       <c r="Y9" s="35"/>
       <c r="Z9" s="35"/>
@@ -6685,7 +6691,7 @@
       </c>
       <c r="G10" s="40">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H10" s="41">
         <f t="shared" si="4"/>
@@ -6725,12 +6731,18 @@
       <c r="Q10" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="R10" s="35"/>
+      <c r="R10" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="S10" s="35"/>
       <c r="T10" s="35"/>
       <c r="U10" s="35"/>
-      <c r="V10" s="35"/>
-      <c r="W10" s="35"/>
+      <c r="V10" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="W10" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X10" s="35"/>
       <c r="Y10" s="35"/>
       <c r="Z10" s="35"/>
@@ -6871,7 +6883,7 @@
       </c>
       <c r="G11" s="40">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H11" s="41">
         <f t="shared" si="4"/>
@@ -6911,12 +6923,18 @@
       <c r="Q11" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="R11" s="35"/>
+      <c r="R11" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="S11" s="35"/>
       <c r="T11" s="35"/>
       <c r="U11" s="35"/>
-      <c r="V11" s="35"/>
-      <c r="W11" s="35"/>
+      <c r="V11" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="W11" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X11" s="35"/>
       <c r="Y11" s="35"/>
       <c r="Z11" s="35"/>
@@ -7057,7 +7075,7 @@
       </c>
       <c r="G12" s="40">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H12" s="41">
         <f t="shared" si="4"/>
@@ -7097,12 +7115,18 @@
       <c r="Q12" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="R12" s="35"/>
+      <c r="R12" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="S12" s="35"/>
       <c r="T12" s="35"/>
       <c r="U12" s="35"/>
-      <c r="V12" s="35"/>
-      <c r="W12" s="35"/>
+      <c r="V12" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="W12" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X12" s="35"/>
       <c r="Y12" s="35"/>
       <c r="Z12" s="35"/>
@@ -7243,7 +7267,7 @@
       </c>
       <c r="G13" s="40">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H13" s="41">
         <f t="shared" si="4"/>
@@ -7283,12 +7307,18 @@
       <c r="Q13" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="R13" s="35"/>
+      <c r="R13" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="S13" s="35"/>
       <c r="T13" s="35"/>
       <c r="U13" s="35"/>
-      <c r="V13" s="35"/>
-      <c r="W13" s="35"/>
+      <c r="V13" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="W13" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X13" s="35"/>
       <c r="Y13" s="35"/>
       <c r="Z13" s="35"/>
@@ -7429,7 +7459,7 @@
       </c>
       <c r="G14" s="40">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H14" s="41">
         <f t="shared" si="4"/>
@@ -7469,12 +7499,18 @@
       <c r="Q14" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="R14" s="35"/>
+      <c r="R14" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="S14" s="35"/>
       <c r="T14" s="35"/>
       <c r="U14" s="35"/>
-      <c r="V14" s="35"/>
-      <c r="W14" s="35"/>
+      <c r="V14" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="W14" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X14" s="35"/>
       <c r="Y14" s="35"/>
       <c r="Z14" s="35"/>
@@ -7615,7 +7651,7 @@
       </c>
       <c r="G15" s="40">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H15" s="41">
         <f t="shared" si="4"/>
@@ -7655,12 +7691,18 @@
       <c r="Q15" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="R15" s="35"/>
+      <c r="R15" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="S15" s="35"/>
       <c r="T15" s="35"/>
       <c r="U15" s="35"/>
-      <c r="V15" s="35"/>
-      <c r="W15" s="35"/>
+      <c r="V15" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="W15" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X15" s="35"/>
       <c r="Y15" s="35"/>
       <c r="Z15" s="35"/>
@@ -7801,7 +7843,7 @@
       </c>
       <c r="G16" s="40">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H16" s="41">
         <f t="shared" si="4"/>
@@ -7841,12 +7883,18 @@
       <c r="Q16" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="R16" s="35"/>
+      <c r="R16" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="S16" s="35"/>
       <c r="T16" s="35"/>
       <c r="U16" s="35"/>
-      <c r="V16" s="35"/>
-      <c r="W16" s="35"/>
+      <c r="V16" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="W16" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X16" s="35"/>
       <c r="Y16" s="35"/>
       <c r="Z16" s="35"/>
@@ -7987,7 +8035,7 @@
       </c>
       <c r="G17" s="40">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H17" s="41">
         <f t="shared" si="4"/>
@@ -8027,12 +8075,18 @@
       <c r="Q17" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="R17" s="35"/>
+      <c r="R17" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="S17" s="35"/>
       <c r="T17" s="35"/>
       <c r="U17" s="35"/>
-      <c r="V17" s="35"/>
-      <c r="W17" s="35"/>
+      <c r="V17" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="W17" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X17" s="35"/>
       <c r="Y17" s="35"/>
       <c r="Z17" s="35"/>
@@ -8173,7 +8227,7 @@
       </c>
       <c r="G18" s="40">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H18" s="41">
         <f t="shared" si="4"/>
@@ -8213,12 +8267,18 @@
       <c r="Q18" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="R18" s="35"/>
+      <c r="R18" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="S18" s="35"/>
       <c r="T18" s="35"/>
       <c r="U18" s="35"/>
-      <c r="V18" s="35"/>
-      <c r="W18" s="35"/>
+      <c r="V18" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="W18" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X18" s="35"/>
       <c r="Y18" s="35"/>
       <c r="Z18" s="35"/>
@@ -8359,7 +8419,7 @@
       </c>
       <c r="G19" s="40">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H19" s="41">
         <f t="shared" si="4"/>
@@ -8399,12 +8459,18 @@
       <c r="Q19" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="R19" s="35"/>
+      <c r="R19" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="S19" s="35"/>
       <c r="T19" s="35"/>
       <c r="U19" s="35"/>
-      <c r="V19" s="35"/>
-      <c r="W19" s="35"/>
+      <c r="V19" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="W19" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X19" s="35"/>
       <c r="Y19" s="35"/>
       <c r="Z19" s="35"/>
@@ -8545,7 +8611,7 @@
       </c>
       <c r="G20" s="40">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H20" s="41">
         <f t="shared" si="4"/>
@@ -8585,12 +8651,18 @@
       <c r="Q20" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="R20" s="35"/>
+      <c r="R20" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="S20" s="35"/>
       <c r="T20" s="35"/>
       <c r="U20" s="35"/>
-      <c r="V20" s="35"/>
-      <c r="W20" s="35"/>
+      <c r="V20" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="W20" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X20" s="35"/>
       <c r="Y20" s="35"/>
       <c r="Z20" s="35"/>
@@ -8729,7 +8801,7 @@
       </c>
       <c r="G21" s="40">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H21" s="41">
         <f t="shared" si="4"/>
@@ -8769,12 +8841,18 @@
       <c r="Q21" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="R21" s="35"/>
+      <c r="R21" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="S21" s="35"/>
       <c r="T21" s="35"/>
       <c r="U21" s="35"/>
-      <c r="V21" s="35"/>
-      <c r="W21" s="35"/>
+      <c r="V21" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="W21" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X21" s="35"/>
       <c r="Y21" s="35"/>
       <c r="Z21" s="35"/>
@@ -8913,7 +8991,7 @@
       </c>
       <c r="G22" s="40">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H22" s="41">
         <f t="shared" si="4"/>
@@ -8953,12 +9031,18 @@
       <c r="Q22" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="R22" s="35"/>
+      <c r="R22" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="S22" s="35"/>
       <c r="T22" s="35"/>
       <c r="U22" s="35"/>
-      <c r="V22" s="35"/>
-      <c r="W22" s="35"/>
+      <c r="V22" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="W22" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X22" s="35"/>
       <c r="Y22" s="35"/>
       <c r="Z22" s="35"/>
@@ -9097,7 +9181,7 @@
       </c>
       <c r="G23" s="40">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H23" s="41">
         <f t="shared" si="4"/>
@@ -9137,12 +9221,18 @@
       <c r="Q23" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="R23" s="35"/>
+      <c r="R23" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="S23" s="35"/>
       <c r="T23" s="35"/>
       <c r="U23" s="35"/>
-      <c r="V23" s="35"/>
-      <c r="W23" s="35"/>
+      <c r="V23" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="W23" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X23" s="35"/>
       <c r="Y23" s="35"/>
       <c r="Z23" s="35"/>
@@ -9281,7 +9371,7 @@
       </c>
       <c r="G24" s="40">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H24" s="41">
         <f t="shared" si="4"/>
@@ -9321,12 +9411,18 @@
       <c r="Q24" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="R24" s="35"/>
+      <c r="R24" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="S24" s="35"/>
       <c r="T24" s="35"/>
       <c r="U24" s="35"/>
-      <c r="V24" s="35"/>
-      <c r="W24" s="35"/>
+      <c r="V24" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="W24" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X24" s="35"/>
       <c r="Y24" s="35"/>
       <c r="Z24" s="35"/>
@@ -9461,11 +9557,11 @@
       </c>
       <c r="F25" s="30" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>CON FALTAS</v>
       </c>
       <c r="G25" s="40">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H25" s="41">
         <f t="shared" si="4"/>
@@ -9473,7 +9569,7 @@
       </c>
       <c r="I25" s="41">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J25" s="41">
         <f t="shared" si="6"/>
@@ -9497,7 +9593,7 @@
       </c>
       <c r="O25" s="42">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="P25" s="35" t="s">
         <v>40</v>
@@ -9505,12 +9601,18 @@
       <c r="Q25" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="R25" s="35"/>
+      <c r="R25" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="S25" s="35"/>
       <c r="T25" s="35"/>
       <c r="U25" s="35"/>
-      <c r="V25" s="35"/>
-      <c r="W25" s="35"/>
+      <c r="V25" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="W25" s="35" t="s">
+        <v>13</v>
+      </c>
       <c r="X25" s="35"/>
       <c r="Y25" s="35"/>
       <c r="Z25" s="35"/>
@@ -9649,7 +9751,7 @@
       </c>
       <c r="G26" s="40">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H26" s="41">
         <f t="shared" si="4"/>
@@ -9689,12 +9791,18 @@
       <c r="Q26" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="R26" s="35"/>
+      <c r="R26" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="S26" s="35"/>
       <c r="T26" s="35"/>
       <c r="U26" s="35"/>
-      <c r="V26" s="35"/>
-      <c r="W26" s="35"/>
+      <c r="V26" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="W26" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X26" s="35"/>
       <c r="Y26" s="35"/>
       <c r="Z26" s="35"/>
@@ -9833,7 +9941,7 @@
       </c>
       <c r="G27" s="40">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H27" s="41">
         <f t="shared" si="4"/>
@@ -9873,12 +9981,18 @@
       <c r="Q27" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="R27" s="35"/>
+      <c r="R27" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="S27" s="35"/>
       <c r="T27" s="35"/>
       <c r="U27" s="35"/>
-      <c r="V27" s="35"/>
-      <c r="W27" s="35"/>
+      <c r="V27" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="W27" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X27" s="35"/>
       <c r="Y27" s="35"/>
       <c r="Z27" s="35"/>
@@ -10017,7 +10131,7 @@
       </c>
       <c r="G28" s="40">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H28" s="41">
         <f t="shared" si="4"/>
@@ -10057,12 +10171,18 @@
       <c r="Q28" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="R28" s="35"/>
+      <c r="R28" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="S28" s="35"/>
       <c r="T28" s="35"/>
       <c r="U28" s="35"/>
-      <c r="V28" s="35"/>
-      <c r="W28" s="35"/>
+      <c r="V28" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="W28" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X28" s="35"/>
       <c r="Y28" s="35"/>
       <c r="Z28" s="35"/>
@@ -10201,7 +10321,7 @@
       </c>
       <c r="G29" s="40">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H29" s="41">
         <f t="shared" si="4"/>
@@ -10241,12 +10361,18 @@
       <c r="Q29" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="R29" s="35"/>
+      <c r="R29" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="S29" s="35"/>
       <c r="T29" s="35"/>
       <c r="U29" s="35"/>
-      <c r="V29" s="35"/>
-      <c r="W29" s="35"/>
+      <c r="V29" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="W29" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X29" s="35"/>
       <c r="Y29" s="35"/>
       <c r="Z29" s="35"/>
@@ -10385,7 +10511,7 @@
       </c>
       <c r="G30" s="40">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H30" s="41">
         <f t="shared" si="4"/>
@@ -10425,12 +10551,18 @@
       <c r="Q30" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="R30" s="35"/>
+      <c r="R30" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="S30" s="35"/>
       <c r="T30" s="35"/>
       <c r="U30" s="35"/>
-      <c r="V30" s="35"/>
-      <c r="W30" s="35"/>
+      <c r="V30" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="W30" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X30" s="35"/>
       <c r="Y30" s="35"/>
       <c r="Z30" s="35"/>
@@ -10568,7 +10700,7 @@
       </c>
       <c r="G31" s="40">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H31" s="41">
         <f t="shared" si="4"/>
@@ -10608,12 +10740,18 @@
       <c r="Q31" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="R31" s="35"/>
+      <c r="R31" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="S31" s="35"/>
       <c r="T31" s="35"/>
       <c r="U31" s="35"/>
-      <c r="V31" s="35"/>
-      <c r="W31" s="35"/>
+      <c r="V31" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="W31" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X31" s="35"/>
       <c r="Y31" s="35"/>
       <c r="Z31" s="35"/>
@@ -10751,7 +10889,7 @@
       </c>
       <c r="G32" s="40">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H32" s="41">
         <f t="shared" si="4"/>
@@ -10791,12 +10929,18 @@
       <c r="Q32" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="R32" s="35"/>
+      <c r="R32" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="S32" s="35"/>
       <c r="T32" s="35"/>
       <c r="U32" s="35"/>
-      <c r="V32" s="35"/>
-      <c r="W32" s="35"/>
+      <c r="V32" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="W32" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X32" s="35"/>
       <c r="Y32" s="35"/>
       <c r="Z32" s="35"/>
@@ -10934,7 +11078,7 @@
       </c>
       <c r="G33" s="40">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H33" s="41">
         <f t="shared" si="4"/>
@@ -10974,12 +11118,18 @@
       <c r="Q33" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="R33" s="35"/>
+      <c r="R33" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="S33" s="35"/>
       <c r="T33" s="35"/>
       <c r="U33" s="35"/>
-      <c r="V33" s="35"/>
-      <c r="W33" s="35"/>
+      <c r="V33" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="W33" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X33" s="35"/>
       <c r="Y33" s="35"/>
       <c r="Z33" s="35"/>
@@ -11117,7 +11267,7 @@
       </c>
       <c r="G34" s="40">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H34" s="41">
         <f t="shared" si="4"/>
@@ -11157,12 +11307,18 @@
       <c r="Q34" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="R34" s="35"/>
+      <c r="R34" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="S34" s="35"/>
       <c r="T34" s="35"/>
       <c r="U34" s="35"/>
-      <c r="V34" s="35"/>
-      <c r="W34" s="35"/>
+      <c r="V34" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="W34" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X34" s="35"/>
       <c r="Y34" s="35"/>
       <c r="Z34" s="35"/>
@@ -11300,7 +11456,7 @@
       </c>
       <c r="G35" s="40">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H35" s="41">
         <f t="shared" si="4"/>
@@ -11340,12 +11496,18 @@
       <c r="Q35" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="R35" s="35"/>
+      <c r="R35" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="S35" s="35"/>
       <c r="T35" s="35"/>
       <c r="U35" s="35"/>
-      <c r="V35" s="35"/>
-      <c r="W35" s="35"/>
+      <c r="V35" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="W35" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X35" s="35"/>
       <c r="Y35" s="35"/>
       <c r="Z35" s="35"/>
@@ -11478,11 +11640,11 @@
       </c>
       <c r="F36" s="30" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>CON FALTAS</v>
       </c>
       <c r="G36" s="40">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H36" s="41">
         <f t="shared" si="4"/>
@@ -11490,7 +11652,7 @@
       </c>
       <c r="I36" s="41">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J36" s="41">
         <f t="shared" si="6"/>
@@ -11514,7 +11676,7 @@
       </c>
       <c r="O36" s="42">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="P36" s="35" t="s">
         <v>40</v>
@@ -11522,12 +11684,18 @@
       <c r="Q36" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="R36" s="35"/>
+      <c r="R36" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="S36" s="35"/>
       <c r="T36" s="35"/>
       <c r="U36" s="35"/>
-      <c r="V36" s="35"/>
-      <c r="W36" s="35"/>
+      <c r="V36" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="W36" s="35" t="s">
+        <v>13</v>
+      </c>
       <c r="X36" s="35"/>
       <c r="Y36" s="35"/>
       <c r="Z36" s="35"/>
@@ -11665,7 +11833,7 @@
       </c>
       <c r="G37" s="40">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H37" s="41">
         <f t="shared" si="4"/>
@@ -11705,12 +11873,18 @@
       <c r="Q37" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="R37" s="35"/>
+      <c r="R37" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="S37" s="35"/>
       <c r="T37" s="35"/>
       <c r="U37" s="35"/>
-      <c r="V37" s="35"/>
-      <c r="W37" s="35"/>
+      <c r="V37" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="W37" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X37" s="35"/>
       <c r="Y37" s="35"/>
       <c r="Z37" s="35"/>
@@ -11848,7 +12022,7 @@
       </c>
       <c r="G38" s="40">
         <f t="shared" ref="G38:G43" si="43">COUNTIF(P38:CR38,"A")</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H38" s="41">
         <f t="shared" ref="H38:H43" si="44">COUNTIF(P38:CR38,"CE")</f>
@@ -11888,12 +12062,18 @@
       <c r="Q38" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="R38" s="35"/>
+      <c r="R38" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="S38" s="35"/>
       <c r="T38" s="35"/>
       <c r="U38" s="35"/>
-      <c r="V38" s="35"/>
-      <c r="W38" s="35"/>
+      <c r="V38" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="W38" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X38" s="35"/>
       <c r="Y38" s="35"/>
       <c r="Z38" s="35"/>
@@ -12025,7 +12205,7 @@
       </c>
       <c r="G39" s="40">
         <f t="shared" si="43"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H39" s="41">
         <f t="shared" si="44"/>
@@ -12065,12 +12245,18 @@
       <c r="Q39" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="R39" s="35"/>
+      <c r="R39" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="S39" s="35"/>
       <c r="T39" s="35"/>
       <c r="U39" s="35"/>
-      <c r="V39" s="35"/>
-      <c r="W39" s="35"/>
+      <c r="V39" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="W39" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X39" s="35"/>
       <c r="Y39" s="35"/>
       <c r="Z39" s="35"/>
@@ -12202,7 +12388,7 @@
       </c>
       <c r="G40" s="40">
         <f t="shared" si="43"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H40" s="41">
         <f t="shared" si="44"/>
@@ -12242,12 +12428,18 @@
       <c r="Q40" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="R40" s="35"/>
+      <c r="R40" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="S40" s="35"/>
       <c r="T40" s="35"/>
       <c r="U40" s="35"/>
-      <c r="V40" s="35"/>
-      <c r="W40" s="35"/>
+      <c r="V40" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="W40" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X40" s="35"/>
       <c r="Y40" s="35"/>
       <c r="Z40" s="35"/>
@@ -12379,7 +12571,7 @@
       </c>
       <c r="G41" s="40">
         <f t="shared" si="43"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H41" s="41">
         <f t="shared" si="44"/>
@@ -12419,12 +12611,18 @@
       <c r="Q41" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="R41" s="35"/>
+      <c r="R41" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="S41" s="35"/>
       <c r="T41" s="35"/>
       <c r="U41" s="35"/>
-      <c r="V41" s="35"/>
-      <c r="W41" s="35"/>
+      <c r="V41" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="W41" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X41" s="35"/>
       <c r="Y41" s="35"/>
       <c r="Z41" s="35"/>
@@ -12556,7 +12754,7 @@
       </c>
       <c r="G42" s="40">
         <f t="shared" si="43"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H42" s="41">
         <f t="shared" si="44"/>
@@ -12596,12 +12794,18 @@
       <c r="Q42" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="R42" s="35"/>
+      <c r="R42" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="S42" s="35"/>
       <c r="T42" s="35"/>
       <c r="U42" s="35"/>
-      <c r="V42" s="35"/>
-      <c r="W42" s="35"/>
+      <c r="V42" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="W42" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X42" s="35"/>
       <c r="Y42" s="35"/>
       <c r="Z42" s="35"/>
@@ -12733,7 +12937,7 @@
       </c>
       <c r="G43" s="40">
         <f t="shared" si="43"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H43" s="41">
         <f t="shared" si="44"/>
@@ -12773,12 +12977,18 @@
       <c r="Q43" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="R43" s="35"/>
+      <c r="R43" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="S43" s="35"/>
       <c r="T43" s="35"/>
       <c r="U43" s="35"/>
-      <c r="V43" s="35"/>
-      <c r="W43" s="35"/>
+      <c r="V43" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="W43" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X43" s="35"/>
       <c r="Y43" s="35"/>
       <c r="Z43" s="35"/>
@@ -12891,20 +13101,20 @@
       <c r="D44" s="75"/>
       <c r="E44" s="75"/>
       <c r="F44" s="74"/>
-      <c r="G44" s="161" t="s">
+      <c r="G44" s="169" t="s">
         <v>61</v>
       </c>
-      <c r="H44" s="122"/>
-      <c r="I44" s="122"/>
-      <c r="J44" s="122"/>
-      <c r="K44" s="122"/>
-      <c r="L44" s="122"/>
-      <c r="M44" s="123"/>
-      <c r="N44" s="124" t="str">
+      <c r="H44" s="130"/>
+      <c r="I44" s="130"/>
+      <c r="J44" s="130"/>
+      <c r="K44" s="130"/>
+      <c r="L44" s="130"/>
+      <c r="M44" s="131"/>
+      <c r="N44" s="132" t="str">
         <f>G8</f>
         <v>A</v>
       </c>
-      <c r="O44" s="125"/>
+      <c r="O44" s="133"/>
       <c r="P44" s="43">
         <f t="shared" ref="P44:AU44" si="52">COUNTIF(P9:P37,"A")</f>
         <v>29</v>
@@ -12915,7 +13125,7 @@
       </c>
       <c r="R44" s="43">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="S44" s="43">
         <f t="shared" si="52"/>
@@ -12931,11 +13141,11 @@
       </c>
       <c r="V44" s="43">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="W44" s="43">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="X44" s="43">
         <f t="shared" si="52"/>
@@ -13289,20 +13499,20 @@
       <c r="D45" s="75"/>
       <c r="E45" s="75"/>
       <c r="F45" s="74"/>
-      <c r="G45" s="131" t="s">
+      <c r="G45" s="139" t="s">
         <v>12</v>
       </c>
-      <c r="H45" s="122"/>
-      <c r="I45" s="122"/>
-      <c r="J45" s="122"/>
-      <c r="K45" s="122"/>
-      <c r="L45" s="122"/>
-      <c r="M45" s="123"/>
-      <c r="N45" s="124" t="str">
+      <c r="H45" s="130"/>
+      <c r="I45" s="130"/>
+      <c r="J45" s="130"/>
+      <c r="K45" s="130"/>
+      <c r="L45" s="130"/>
+      <c r="M45" s="131"/>
+      <c r="N45" s="132" t="str">
         <f>H8</f>
         <v>CE</v>
       </c>
-      <c r="O45" s="125"/>
+      <c r="O45" s="133"/>
       <c r="P45" s="43">
         <f t="shared" ref="P45:AU45" si="56">COUNTIF(P9:P37,"CE")</f>
         <v>0</v>
@@ -13687,20 +13897,20 @@
       <c r="D46" s="75"/>
       <c r="E46" s="75"/>
       <c r="F46" s="74"/>
-      <c r="G46" s="132" t="s">
+      <c r="G46" s="140" t="s">
         <v>14</v>
       </c>
-      <c r="H46" s="122"/>
-      <c r="I46" s="122"/>
-      <c r="J46" s="122"/>
-      <c r="K46" s="122"/>
-      <c r="L46" s="122"/>
-      <c r="M46" s="123"/>
-      <c r="N46" s="124" t="str">
+      <c r="H46" s="130"/>
+      <c r="I46" s="130"/>
+      <c r="J46" s="130"/>
+      <c r="K46" s="130"/>
+      <c r="L46" s="130"/>
+      <c r="M46" s="131"/>
+      <c r="N46" s="132" t="str">
         <f>I8</f>
         <v>SE</v>
       </c>
-      <c r="O46" s="125"/>
+      <c r="O46" s="133"/>
       <c r="P46" s="43">
         <f t="shared" ref="P46:AU46" si="60">COUNTIF(P9:P37,"SE")</f>
         <v>0</v>
@@ -13727,11 +13937,11 @@
       </c>
       <c r="V46" s="43">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W46" s="43">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X46" s="43">
         <f t="shared" si="60"/>
@@ -14085,20 +14295,20 @@
       <c r="D47" s="75"/>
       <c r="E47" s="75"/>
       <c r="F47" s="44"/>
-      <c r="G47" s="133" t="s">
+      <c r="G47" s="141" t="s">
         <v>62</v>
       </c>
-      <c r="H47" s="122"/>
-      <c r="I47" s="122"/>
-      <c r="J47" s="122"/>
-      <c r="K47" s="122"/>
-      <c r="L47" s="122"/>
-      <c r="M47" s="123"/>
-      <c r="N47" s="124" t="str">
+      <c r="H47" s="130"/>
+      <c r="I47" s="130"/>
+      <c r="J47" s="130"/>
+      <c r="K47" s="130"/>
+      <c r="L47" s="130"/>
+      <c r="M47" s="131"/>
+      <c r="N47" s="132" t="str">
         <f>J8</f>
         <v>INC</v>
       </c>
-      <c r="O47" s="125"/>
+      <c r="O47" s="133"/>
       <c r="P47" s="43">
         <f t="shared" ref="P47:AU47" si="64">COUNTIF(P9:P37,"INC")</f>
         <v>0</v>
@@ -14483,20 +14693,20 @@
       <c r="D48" s="75"/>
       <c r="E48" s="75"/>
       <c r="F48" s="74"/>
-      <c r="G48" s="128" t="s">
+      <c r="G48" s="136" t="s">
         <v>63</v>
       </c>
-      <c r="H48" s="122"/>
-      <c r="I48" s="122"/>
-      <c r="J48" s="122"/>
-      <c r="K48" s="122"/>
-      <c r="L48" s="122"/>
-      <c r="M48" s="123"/>
-      <c r="N48" s="124" t="str">
+      <c r="H48" s="130"/>
+      <c r="I48" s="130"/>
+      <c r="J48" s="130"/>
+      <c r="K48" s="130"/>
+      <c r="L48" s="130"/>
+      <c r="M48" s="131"/>
+      <c r="N48" s="132" t="str">
         <f>K8</f>
         <v>LIC</v>
       </c>
-      <c r="O48" s="125"/>
+      <c r="O48" s="133"/>
       <c r="P48" s="43">
         <f t="shared" ref="P48:AU48" si="68">COUNTIF(P9:P37,"LIC")</f>
         <v>0</v>
@@ -14881,20 +15091,20 @@
       <c r="D49" s="75"/>
       <c r="E49" s="75"/>
       <c r="F49" s="74"/>
-      <c r="G49" s="121" t="s">
+      <c r="G49" s="129" t="s">
         <v>64</v>
       </c>
-      <c r="H49" s="122"/>
-      <c r="I49" s="122"/>
-      <c r="J49" s="122"/>
-      <c r="K49" s="122"/>
-      <c r="L49" s="122"/>
-      <c r="M49" s="123"/>
-      <c r="N49" s="124" t="str">
+      <c r="H49" s="130"/>
+      <c r="I49" s="130"/>
+      <c r="J49" s="130"/>
+      <c r="K49" s="130"/>
+      <c r="L49" s="130"/>
+      <c r="M49" s="131"/>
+      <c r="N49" s="132" t="str">
         <f>L8</f>
         <v>CLM</v>
       </c>
-      <c r="O49" s="125"/>
+      <c r="O49" s="133"/>
       <c r="P49" s="43">
         <f t="shared" ref="P49:AU49" si="72">COUNTIF(P9:P37,"CLM")</f>
         <v>0</v>
@@ -15279,20 +15489,20 @@
       <c r="D50" s="75"/>
       <c r="E50" s="75"/>
       <c r="F50" s="74"/>
-      <c r="G50" s="126" t="s">
+      <c r="G50" s="134" t="s">
         <v>65</v>
       </c>
-      <c r="H50" s="122"/>
-      <c r="I50" s="122"/>
-      <c r="J50" s="122"/>
-      <c r="K50" s="122"/>
-      <c r="L50" s="122"/>
-      <c r="M50" s="123"/>
-      <c r="N50" s="124" t="str">
+      <c r="H50" s="130"/>
+      <c r="I50" s="130"/>
+      <c r="J50" s="130"/>
+      <c r="K50" s="130"/>
+      <c r="L50" s="130"/>
+      <c r="M50" s="131"/>
+      <c r="N50" s="132" t="str">
         <f>M8</f>
         <v>SFF</v>
       </c>
-      <c r="O50" s="125"/>
+      <c r="O50" s="133"/>
       <c r="P50" s="43">
         <f t="shared" ref="P50:AU50" si="76">COUNTIF(P9:P37,"SFF")</f>
         <v>0</v>
@@ -15677,20 +15887,20 @@
       <c r="D51" s="75"/>
       <c r="E51" s="75"/>
       <c r="F51" s="74"/>
-      <c r="G51" s="127" t="s">
+      <c r="G51" s="135" t="s">
         <v>66</v>
       </c>
-      <c r="H51" s="122"/>
-      <c r="I51" s="122"/>
-      <c r="J51" s="122"/>
-      <c r="K51" s="122"/>
-      <c r="L51" s="122"/>
-      <c r="M51" s="123"/>
-      <c r="N51" s="124" t="str">
+      <c r="H51" s="130"/>
+      <c r="I51" s="130"/>
+      <c r="J51" s="130"/>
+      <c r="K51" s="130"/>
+      <c r="L51" s="130"/>
+      <c r="M51" s="131"/>
+      <c r="N51" s="132" t="str">
         <f>N8</f>
         <v>RET</v>
       </c>
-      <c r="O51" s="125"/>
+      <c r="O51" s="133"/>
       <c r="P51" s="43">
         <f t="shared" ref="P51:AU51" si="80">COUNTIF(P9:P37,"RET")</f>
         <v>0</v>
@@ -41476,18 +41686,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A1" s="164">
-        <v>0</v>
-      </c>
-      <c r="B1" s="108"/>
-      <c r="C1" s="108"/>
-      <c r="D1" s="108"/>
-      <c r="E1" s="108"/>
-      <c r="F1" s="108"/>
-      <c r="G1" s="108"/>
-      <c r="H1" s="108"/>
-      <c r="I1" s="108"/>
-      <c r="J1" s="94"/>
+      <c r="A1" s="182">
+        <v>0</v>
+      </c>
+      <c r="B1" s="116"/>
+      <c r="C1" s="116"/>
+      <c r="D1" s="116"/>
+      <c r="E1" s="116"/>
+      <c r="F1" s="116"/>
+      <c r="G1" s="116"/>
+      <c r="H1" s="116"/>
+      <c r="I1" s="116"/>
+      <c r="J1" s="102"/>
       <c r="L1" s="48"/>
       <c r="M1" s="48"/>
       <c r="N1" s="48"/>
@@ -41505,16 +41715,16 @@
       <c r="Z1" s="48"/>
     </row>
     <row r="2" spans="1:26" ht="15.75">
-      <c r="A2" s="108"/>
-      <c r="B2" s="108"/>
-      <c r="C2" s="108"/>
-      <c r="D2" s="108"/>
-      <c r="E2" s="108"/>
-      <c r="F2" s="108"/>
-      <c r="G2" s="108"/>
-      <c r="H2" s="108"/>
-      <c r="I2" s="108"/>
-      <c r="J2" s="94"/>
+      <c r="A2" s="116"/>
+      <c r="B2" s="116"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
+      <c r="E2" s="116"/>
+      <c r="F2" s="116"/>
+      <c r="G2" s="116"/>
+      <c r="H2" s="116"/>
+      <c r="I2" s="116"/>
+      <c r="J2" s="102"/>
       <c r="L2" s="48"/>
       <c r="M2" s="48"/>
       <c r="N2" s="48"/>
@@ -41532,15 +41742,15 @@
       <c r="Z2" s="48"/>
     </row>
     <row r="3" spans="1:26" ht="15.75">
-      <c r="A3" s="162" t="s">
+      <c r="A3" s="170" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="138"/>
-      <c r="C3" s="165" t="s">
+      <c r="B3" s="146"/>
+      <c r="C3" s="183" t="s">
         <v>59</v>
       </c>
-      <c r="D3" s="88"/>
-      <c r="E3" s="138"/>
+      <c r="D3" s="96"/>
+      <c r="E3" s="146"/>
       <c r="F3" s="49"/>
       <c r="G3" s="49"/>
       <c r="H3" s="50"/>
@@ -41564,15 +41774,15 @@
       <c r="Z3" s="48"/>
     </row>
     <row r="4" spans="1:26" ht="15.75">
-      <c r="A4" s="162" t="s">
+      <c r="A4" s="170" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="138"/>
-      <c r="C4" s="170">
+      <c r="B4" s="146"/>
+      <c r="C4" s="184">
         <v>3458742</v>
       </c>
-      <c r="D4" s="171"/>
-      <c r="E4" s="172"/>
+      <c r="D4" s="185"/>
+      <c r="E4" s="186"/>
       <c r="F4" s="51" t="s">
         <v>67</v>
       </c>
@@ -41602,15 +41812,15 @@
       <c r="Z4" s="48"/>
     </row>
     <row r="5" spans="1:26" ht="15.75">
-      <c r="A5" s="162" t="s">
+      <c r="A5" s="170" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="138"/>
-      <c r="C5" s="173" t="s">
+      <c r="B5" s="146"/>
+      <c r="C5" s="179" t="s">
         <v>97</v>
       </c>
-      <c r="D5" s="174"/>
-      <c r="E5" s="175"/>
+      <c r="D5" s="180"/>
+      <c r="E5" s="181"/>
       <c r="F5" s="51" t="s">
         <v>69</v>
       </c>
@@ -41638,15 +41848,15 @@
       <c r="Z5" s="48"/>
     </row>
     <row r="6" spans="1:26" ht="15.75">
-      <c r="A6" s="162" t="s">
+      <c r="A6" s="170" t="s">
         <v>70</v>
       </c>
-      <c r="B6" s="138"/>
-      <c r="C6" s="176" t="s">
+      <c r="B6" s="146"/>
+      <c r="C6" s="171" t="s">
         <v>98</v>
       </c>
-      <c r="D6" s="177"/>
-      <c r="E6" s="178"/>
+      <c r="D6" s="172"/>
+      <c r="E6" s="173"/>
       <c r="F6" s="51" t="s">
         <v>71</v>
       </c>
@@ -41674,15 +41884,15 @@
       <c r="Z6" s="48"/>
     </row>
     <row r="7" spans="1:26" ht="15.75">
-      <c r="A7" s="162" t="s">
+      <c r="A7" s="170" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="138"/>
-      <c r="C7" s="179" t="s">
+      <c r="B7" s="146"/>
+      <c r="C7" s="174" t="s">
         <v>99</v>
       </c>
-      <c r="D7" s="180"/>
-      <c r="E7" s="181"/>
+      <c r="D7" s="175"/>
+      <c r="E7" s="176"/>
       <c r="F7" s="55" t="s">
         <v>72</v>
       </c>
@@ -41710,17 +41920,17 @@
       <c r="Z7" s="48"/>
     </row>
     <row r="8" spans="1:26" ht="15.75">
-      <c r="A8" s="163" t="s">
+      <c r="A8" s="177" t="s">
         <v>73</v>
       </c>
-      <c r="B8" s="138"/>
-      <c r="C8" s="182" t="s">
+      <c r="B8" s="146"/>
+      <c r="C8" s="178" t="s">
         <v>100</v>
       </c>
-      <c r="D8" s="88"/>
-      <c r="E8" s="88"/>
-      <c r="F8" s="88"/>
-      <c r="G8" s="138"/>
+      <c r="D8" s="96"/>
+      <c r="E8" s="96"/>
+      <c r="F8" s="96"/>
+      <c r="G8" s="146"/>
       <c r="H8" s="50"/>
       <c r="I8" s="50"/>
       <c r="J8" s="48"/>
@@ -41795,32 +42005,32 @@
       <c r="A10" s="77">
         <v>1</v>
       </c>
-      <c r="B10" s="185" t="s">
+      <c r="B10" s="84" t="s">
         <v>101</v>
       </c>
-      <c r="C10" s="186" t="s">
+      <c r="C10" s="85" t="s">
         <v>92</v>
       </c>
-      <c r="D10" s="185">
+      <c r="D10" s="84">
         <v>1145225853</v>
       </c>
-      <c r="E10" s="187"/>
-      <c r="F10" s="187" t="s">
+      <c r="E10" s="86"/>
+      <c r="F10" s="86" t="s">
         <v>102</v>
       </c>
-      <c r="G10" s="185">
+      <c r="G10" s="84">
         <v>3122987449</v>
       </c>
-      <c r="H10" s="185" t="s">
+      <c r="H10" s="84" t="s">
         <v>103</v>
       </c>
-      <c r="I10" s="187" t="s">
+      <c r="I10" s="86" t="s">
         <v>104</v>
       </c>
-      <c r="J10" s="185">
+      <c r="J10" s="84">
         <v>3214591164</v>
       </c>
-      <c r="K10" s="187" t="s">
+      <c r="K10" s="86" t="s">
         <v>105</v>
       </c>
       <c r="L10" s="48"/>
@@ -41844,32 +42054,32 @@
         <f t="shared" ref="A11:A45" si="0">A10+1</f>
         <v>2</v>
       </c>
-      <c r="B11" s="188" t="s">
+      <c r="B11" s="87" t="s">
         <v>106</v>
       </c>
-      <c r="C11" s="189" t="s">
+      <c r="C11" s="88" t="s">
         <v>92</v>
       </c>
-      <c r="D11" s="188">
+      <c r="D11" s="87">
         <v>1145225854</v>
       </c>
-      <c r="E11" s="190"/>
-      <c r="F11" s="190" t="s">
+      <c r="E11" s="89"/>
+      <c r="F11" s="89" t="s">
         <v>107</v>
       </c>
-      <c r="G11" s="188">
+      <c r="G11" s="87">
         <v>3214127416</v>
       </c>
-      <c r="H11" s="188" t="s">
+      <c r="H11" s="87" t="s">
         <v>103</v>
       </c>
-      <c r="I11" s="190" t="s">
+      <c r="I11" s="89" t="s">
         <v>104</v>
       </c>
-      <c r="J11" s="188">
+      <c r="J11" s="87">
         <v>3214591164</v>
       </c>
-      <c r="K11" s="190" t="s">
+      <c r="K11" s="89" t="s">
         <v>108</v>
       </c>
       <c r="L11" s="48"/>
@@ -41895,32 +42105,32 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B12" s="185" t="s">
+      <c r="B12" s="84" t="s">
         <v>109</v>
       </c>
-      <c r="C12" s="186" t="s">
+      <c r="C12" s="85" t="s">
         <v>92</v>
       </c>
-      <c r="D12" s="185">
+      <c r="D12" s="84">
         <v>1019068647</v>
       </c>
-      <c r="E12" s="187"/>
-      <c r="F12" s="187" t="s">
+      <c r="E12" s="86"/>
+      <c r="F12" s="86" t="s">
         <v>110</v>
       </c>
-      <c r="G12" s="185">
+      <c r="G12" s="84">
         <v>3118627706</v>
       </c>
-      <c r="H12" s="185" t="s">
+      <c r="H12" s="84" t="s">
         <v>111</v>
       </c>
-      <c r="I12" s="187" t="s">
+      <c r="I12" s="86" t="s">
         <v>112</v>
       </c>
-      <c r="J12" s="185">
+      <c r="J12" s="84">
         <v>3244956518</v>
       </c>
-      <c r="K12" s="187" t="s">
+      <c r="K12" s="86" t="s">
         <v>113</v>
       </c>
       <c r="L12" s="48"/>
@@ -41944,32 +42154,32 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B13" s="188" t="s">
+      <c r="B13" s="87" t="s">
         <v>114</v>
       </c>
-      <c r="C13" s="189" t="s">
+      <c r="C13" s="88" t="s">
         <v>92</v>
       </c>
-      <c r="D13" s="188">
+      <c r="D13" s="87">
         <v>1015437646</v>
       </c>
-      <c r="E13" s="190"/>
-      <c r="F13" s="190" t="s">
+      <c r="E13" s="89"/>
+      <c r="F13" s="89" t="s">
         <v>115</v>
       </c>
-      <c r="G13" s="188">
+      <c r="G13" s="87">
         <v>3219658075</v>
       </c>
-      <c r="H13" s="188" t="s">
+      <c r="H13" s="87" t="s">
         <v>116</v>
       </c>
-      <c r="I13" s="190" t="s">
+      <c r="I13" s="89" t="s">
         <v>117</v>
       </c>
-      <c r="J13" s="188">
+      <c r="J13" s="87">
         <v>3112776462</v>
       </c>
-      <c r="K13" s="190" t="s">
+      <c r="K13" s="89" t="s">
         <v>118</v>
       </c>
       <c r="L13" s="48"/>
@@ -41993,32 +42203,32 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B14" s="185" t="s">
+      <c r="B14" s="84" t="s">
         <v>119</v>
       </c>
-      <c r="C14" s="186" t="s">
+      <c r="C14" s="85" t="s">
         <v>92</v>
       </c>
-      <c r="D14" s="185">
+      <c r="D14" s="84">
         <v>1141123667</v>
       </c>
-      <c r="E14" s="187"/>
-      <c r="F14" s="187" t="s">
+      <c r="E14" s="86"/>
+      <c r="F14" s="86" t="s">
         <v>120</v>
       </c>
-      <c r="G14" s="185">
+      <c r="G14" s="84">
         <v>3134883535</v>
       </c>
-      <c r="H14" s="185" t="s">
+      <c r="H14" s="84" t="s">
         <v>121</v>
       </c>
-      <c r="I14" s="187" t="s">
+      <c r="I14" s="86" t="s">
         <v>122</v>
       </c>
-      <c r="J14" s="185">
+      <c r="J14" s="84">
         <v>3219273385</v>
       </c>
-      <c r="K14" s="187" t="s">
+      <c r="K14" s="86" t="s">
         <v>123</v>
       </c>
       <c r="L14" s="48"/>
@@ -42042,32 +42252,32 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B15" s="188" t="s">
+      <c r="B15" s="87" t="s">
         <v>124</v>
       </c>
-      <c r="C15" s="189" t="s">
+      <c r="C15" s="88" t="s">
         <v>125</v>
       </c>
-      <c r="D15" s="188">
+      <c r="D15" s="87">
         <v>1014206476</v>
       </c>
-      <c r="E15" s="190"/>
-      <c r="F15" s="190" t="s">
+      <c r="E15" s="89"/>
+      <c r="F15" s="89" t="s">
         <v>126</v>
       </c>
-      <c r="G15" s="188">
+      <c r="G15" s="87">
         <v>3012776831</v>
       </c>
-      <c r="H15" s="188" t="s">
+      <c r="H15" s="87" t="s">
         <v>127</v>
       </c>
-      <c r="I15" s="190" t="s">
+      <c r="I15" s="89" t="s">
         <v>128</v>
       </c>
-      <c r="J15" s="188">
+      <c r="J15" s="87">
         <v>3012699148</v>
       </c>
-      <c r="K15" s="190" t="s">
+      <c r="K15" s="89" t="s">
         <v>129</v>
       </c>
       <c r="L15" s="48"/>
@@ -42091,32 +42301,32 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B16" s="185" t="s">
+      <c r="B16" s="84" t="s">
         <v>130</v>
       </c>
-      <c r="C16" s="186" t="s">
+      <c r="C16" s="85" t="s">
         <v>92</v>
       </c>
-      <c r="D16" s="185">
+      <c r="D16" s="84">
         <v>1141120978</v>
       </c>
-      <c r="E16" s="187"/>
-      <c r="F16" s="187" t="s">
+      <c r="E16" s="86"/>
+      <c r="F16" s="86" t="s">
         <v>131</v>
       </c>
-      <c r="G16" s="185">
+      <c r="G16" s="84">
         <v>3193860120</v>
       </c>
-      <c r="H16" s="185" t="s">
+      <c r="H16" s="84" t="s">
         <v>132</v>
       </c>
-      <c r="I16" s="187" t="s">
+      <c r="I16" s="86" t="s">
         <v>133</v>
       </c>
-      <c r="J16" s="185">
+      <c r="J16" s="84">
         <v>3138165624</v>
       </c>
-      <c r="K16" s="187" t="s">
+      <c r="K16" s="86" t="s">
         <v>134</v>
       </c>
       <c r="L16" s="48"/>
@@ -42140,32 +42350,32 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B17" s="188" t="s">
+      <c r="B17" s="87" t="s">
         <v>135</v>
       </c>
-      <c r="C17" s="189" t="s">
+      <c r="C17" s="88" t="s">
         <v>92</v>
       </c>
-      <c r="D17" s="188">
+      <c r="D17" s="87">
         <v>1028493847</v>
       </c>
-      <c r="E17" s="190"/>
-      <c r="F17" s="190" t="s">
+      <c r="E17" s="89"/>
+      <c r="F17" s="89" t="s">
         <v>136</v>
       </c>
-      <c r="G17" s="188">
+      <c r="G17" s="87">
         <v>3143693010</v>
       </c>
-      <c r="H17" s="188" t="s">
+      <c r="H17" s="87" t="s">
         <v>137</v>
       </c>
-      <c r="I17" s="190" t="s">
+      <c r="I17" s="89" t="s">
         <v>138</v>
       </c>
-      <c r="J17" s="188">
+      <c r="J17" s="87">
         <v>3102683294</v>
       </c>
-      <c r="K17" s="190" t="s">
+      <c r="K17" s="89" t="s">
         <v>139</v>
       </c>
       <c r="L17" s="48"/>
@@ -42189,32 +42399,32 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B18" s="185" t="s">
+      <c r="B18" s="84" t="s">
         <v>140</v>
       </c>
-      <c r="C18" s="186" t="s">
+      <c r="C18" s="85" t="s">
         <v>92</v>
       </c>
-      <c r="D18" s="185">
+      <c r="D18" s="84">
         <v>1031825573</v>
       </c>
-      <c r="E18" s="187"/>
-      <c r="F18" s="187" t="s">
+      <c r="E18" s="86"/>
+      <c r="F18" s="86" t="s">
         <v>141</v>
       </c>
-      <c r="G18" s="185">
+      <c r="G18" s="84">
         <v>3228981740</v>
       </c>
-      <c r="H18" s="185" t="s">
+      <c r="H18" s="84" t="s">
         <v>142</v>
       </c>
-      <c r="I18" s="187" t="s">
+      <c r="I18" s="86" t="s">
         <v>141</v>
       </c>
-      <c r="J18" s="185">
+      <c r="J18" s="84">
         <v>3227484121</v>
       </c>
-      <c r="K18" s="187" t="s">
+      <c r="K18" s="86" t="s">
         <v>143</v>
       </c>
       <c r="L18" s="48"/>
@@ -42238,32 +42448,32 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B19" s="188" t="s">
+      <c r="B19" s="87" t="s">
         <v>144</v>
       </c>
-      <c r="C19" s="189" t="s">
+      <c r="C19" s="88" t="s">
         <v>92</v>
       </c>
-      <c r="D19" s="188">
+      <c r="D19" s="87">
         <v>1145927122</v>
       </c>
-      <c r="E19" s="190"/>
-      <c r="F19" s="190" t="s">
+      <c r="E19" s="89"/>
+      <c r="F19" s="89" t="s">
         <v>145</v>
       </c>
-      <c r="G19" s="188">
+      <c r="G19" s="87">
         <v>3219741619</v>
       </c>
-      <c r="H19" s="188" t="s">
+      <c r="H19" s="87" t="s">
         <v>146</v>
       </c>
-      <c r="I19" s="190" t="s">
+      <c r="I19" s="89" t="s">
         <v>147</v>
       </c>
-      <c r="J19" s="188">
+      <c r="J19" s="87">
         <v>3014904232</v>
       </c>
-      <c r="K19" s="190" t="s">
+      <c r="K19" s="89" t="s">
         <v>148</v>
       </c>
       <c r="L19" s="48"/>
@@ -42287,32 +42497,32 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B20" s="185" t="s">
+      <c r="B20" s="84" t="s">
         <v>149</v>
       </c>
-      <c r="C20" s="186" t="s">
+      <c r="C20" s="85" t="s">
         <v>92</v>
       </c>
-      <c r="D20" s="185">
+      <c r="D20" s="84">
         <v>1141123455</v>
       </c>
-      <c r="E20" s="187"/>
-      <c r="F20" s="187" t="s">
+      <c r="E20" s="86"/>
+      <c r="F20" s="86" t="s">
         <v>150</v>
       </c>
-      <c r="G20" s="185">
+      <c r="G20" s="84">
         <v>3212390849</v>
       </c>
-      <c r="H20" s="185" t="s">
+      <c r="H20" s="84" t="s">
         <v>151</v>
       </c>
-      <c r="I20" s="187" t="s">
+      <c r="I20" s="86" t="s">
         <v>152</v>
       </c>
-      <c r="J20" s="185">
+      <c r="J20" s="84">
         <v>3142678128</v>
       </c>
-      <c r="K20" s="187" t="s">
+      <c r="K20" s="86" t="s">
         <v>153</v>
       </c>
       <c r="L20" s="48"/>
@@ -42338,32 +42548,32 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B21" s="188" t="s">
+      <c r="B21" s="87" t="s">
         <v>154</v>
       </c>
-      <c r="C21" s="189" t="s">
+      <c r="C21" s="88" t="s">
         <v>92</v>
       </c>
-      <c r="D21" s="188">
+      <c r="D21" s="87">
         <v>1072990502</v>
       </c>
-      <c r="E21" s="190"/>
-      <c r="F21" s="190" t="s">
+      <c r="E21" s="89"/>
+      <c r="F21" s="89" t="s">
         <v>155</v>
       </c>
-      <c r="G21" s="188">
+      <c r="G21" s="87">
         <v>3204845703</v>
       </c>
-      <c r="H21" s="188" t="s">
+      <c r="H21" s="87" t="s">
         <v>156</v>
       </c>
-      <c r="I21" s="190" t="s">
+      <c r="I21" s="89" t="s">
         <v>157</v>
       </c>
-      <c r="J21" s="188">
+      <c r="J21" s="87">
         <v>3108793726</v>
       </c>
-      <c r="K21" s="190" t="s">
+      <c r="K21" s="89" t="s">
         <v>158</v>
       </c>
       <c r="L21" s="48"/>
@@ -42387,32 +42597,32 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B22" s="185" t="s">
+      <c r="B22" s="84" t="s">
         <v>159</v>
       </c>
-      <c r="C22" s="186" t="s">
+      <c r="C22" s="85" t="s">
         <v>92</v>
       </c>
-      <c r="D22" s="185">
+      <c r="D22" s="84">
         <v>1141121806</v>
       </c>
-      <c r="E22" s="187"/>
-      <c r="F22" s="187" t="s">
+      <c r="E22" s="86"/>
+      <c r="F22" s="86" t="s">
         <v>160</v>
       </c>
-      <c r="G22" s="185">
+      <c r="G22" s="84">
         <v>3204935064</v>
       </c>
-      <c r="H22" s="185" t="s">
+      <c r="H22" s="84" t="s">
         <v>161</v>
       </c>
-      <c r="I22" s="187" t="s">
+      <c r="I22" s="86" t="s">
         <v>162</v>
       </c>
-      <c r="J22" s="185">
+      <c r="J22" s="84">
         <v>3115093949</v>
       </c>
-      <c r="K22" s="187" t="s">
+      <c r="K22" s="86" t="s">
         <v>163</v>
       </c>
       <c r="L22" s="48"/>
@@ -42436,32 +42646,32 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B23" s="188" t="s">
+      <c r="B23" s="87" t="s">
         <v>164</v>
       </c>
-      <c r="C23" s="189" t="s">
+      <c r="C23" s="88" t="s">
         <v>92</v>
       </c>
-      <c r="D23" s="188">
+      <c r="D23" s="87">
         <v>1141121807</v>
       </c>
-      <c r="E23" s="190"/>
-      <c r="F23" s="190" t="s">
+      <c r="E23" s="89"/>
+      <c r="F23" s="89" t="s">
         <v>165</v>
       </c>
-      <c r="G23" s="188">
+      <c r="G23" s="87">
         <v>3219922810</v>
       </c>
-      <c r="H23" s="188" t="s">
+      <c r="H23" s="87" t="s">
         <v>166</v>
       </c>
-      <c r="I23" s="190" t="s">
+      <c r="I23" s="89" t="s">
         <v>167</v>
       </c>
-      <c r="J23" s="188">
+      <c r="J23" s="87">
         <v>3115093949</v>
       </c>
-      <c r="K23" s="190" t="s">
+      <c r="K23" s="89" t="s">
         <v>168</v>
       </c>
       <c r="L23" s="48"/>
@@ -42487,32 +42697,32 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B24" s="185" t="s">
+      <c r="B24" s="84" t="s">
         <v>169</v>
       </c>
-      <c r="C24" s="186" t="s">
+      <c r="C24" s="85" t="s">
         <v>92</v>
       </c>
-      <c r="D24" s="185">
+      <c r="D24" s="84">
         <v>1016043063</v>
       </c>
-      <c r="E24" s="187"/>
-      <c r="F24" s="187" t="s">
+      <c r="E24" s="86"/>
+      <c r="F24" s="86" t="s">
         <v>170</v>
       </c>
-      <c r="G24" s="185">
+      <c r="G24" s="84">
         <v>3159789153</v>
       </c>
-      <c r="H24" s="185" t="s">
+      <c r="H24" s="84" t="s">
         <v>171</v>
       </c>
-      <c r="I24" s="187" t="s">
+      <c r="I24" s="86" t="s">
         <v>170</v>
       </c>
-      <c r="J24" s="185">
+      <c r="J24" s="84">
         <v>3171211281</v>
       </c>
-      <c r="K24" s="187" t="s">
+      <c r="K24" s="86" t="s">
         <v>172</v>
       </c>
       <c r="L24" s="48"/>
@@ -42538,32 +42748,32 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B25" s="188" t="s">
+      <c r="B25" s="87" t="s">
         <v>173</v>
       </c>
-      <c r="C25" s="189" t="s">
+      <c r="C25" s="88" t="s">
         <v>92</v>
       </c>
-      <c r="D25" s="188">
+      <c r="D25" s="87">
         <v>1016033641</v>
       </c>
-      <c r="E25" s="190"/>
-      <c r="F25" s="190" t="s">
+      <c r="E25" s="89"/>
+      <c r="F25" s="89" t="s">
         <v>174</v>
       </c>
-      <c r="G25" s="188">
+      <c r="G25" s="87">
         <v>3223692079</v>
       </c>
-      <c r="H25" s="188" t="s">
+      <c r="H25" s="87" t="s">
         <v>175</v>
       </c>
-      <c r="I25" s="190" t="s">
+      <c r="I25" s="89" t="s">
         <v>176</v>
       </c>
-      <c r="J25" s="188">
+      <c r="J25" s="87">
         <v>3134082226</v>
       </c>
-      <c r="K25" s="190" t="s">
+      <c r="K25" s="89" t="s">
         <v>177</v>
       </c>
       <c r="L25" s="59"/>
@@ -42587,32 +42797,32 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B26" s="185" t="s">
+      <c r="B26" s="84" t="s">
         <v>178</v>
       </c>
-      <c r="C26" s="186" t="s">
+      <c r="C26" s="85" t="s">
         <v>92</v>
       </c>
-      <c r="D26" s="185">
+      <c r="D26" s="84">
         <v>1028888399</v>
       </c>
-      <c r="E26" s="187"/>
-      <c r="F26" s="187" t="s">
+      <c r="E26" s="86"/>
+      <c r="F26" s="86" t="s">
         <v>179</v>
       </c>
-      <c r="G26" s="185">
+      <c r="G26" s="84">
         <v>3228100232</v>
       </c>
-      <c r="H26" s="185" t="s">
+      <c r="H26" s="84" t="s">
         <v>180</v>
       </c>
-      <c r="I26" s="187" t="s">
+      <c r="I26" s="86" t="s">
         <v>181</v>
       </c>
-      <c r="J26" s="185">
+      <c r="J26" s="84">
         <v>3169263822</v>
       </c>
-      <c r="K26" s="187" t="s">
+      <c r="K26" s="86" t="s">
         <v>182</v>
       </c>
       <c r="L26" s="48"/>
@@ -42638,32 +42848,32 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B27" s="188" t="s">
+      <c r="B27" s="87" t="s">
         <v>183</v>
       </c>
-      <c r="C27" s="189" t="s">
+      <c r="C27" s="88" t="s">
         <v>92</v>
       </c>
-      <c r="D27" s="188">
+      <c r="D27" s="87">
         <v>1016956103</v>
       </c>
-      <c r="E27" s="190"/>
-      <c r="F27" s="190" t="s">
+      <c r="E27" s="89"/>
+      <c r="F27" s="89" t="s">
         <v>184</v>
       </c>
-      <c r="G27" s="188">
+      <c r="G27" s="87">
         <v>3204962979</v>
       </c>
-      <c r="H27" s="188" t="s">
+      <c r="H27" s="87" t="s">
         <v>185</v>
       </c>
-      <c r="I27" s="190" t="s">
+      <c r="I27" s="89" t="s">
         <v>186</v>
       </c>
-      <c r="J27" s="188">
+      <c r="J27" s="87">
         <v>3144845401</v>
       </c>
-      <c r="K27" s="190" t="s">
+      <c r="K27" s="89" t="s">
         <v>187</v>
       </c>
       <c r="L27" s="48"/>
@@ -42687,32 +42897,32 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B28" s="185" t="s">
+      <c r="B28" s="84" t="s">
         <v>188</v>
       </c>
-      <c r="C28" s="186" t="s">
+      <c r="C28" s="85" t="s">
         <v>92</v>
       </c>
-      <c r="D28" s="185">
+      <c r="D28" s="84">
         <v>1141125073</v>
       </c>
-      <c r="E28" s="187"/>
-      <c r="F28" s="187" t="s">
+      <c r="E28" s="86"/>
+      <c r="F28" s="86" t="s">
         <v>189</v>
       </c>
-      <c r="G28" s="185">
+      <c r="G28" s="84">
         <v>3246343302</v>
       </c>
-      <c r="H28" s="185" t="s">
+      <c r="H28" s="84" t="s">
         <v>190</v>
       </c>
-      <c r="I28" s="187" t="s">
+      <c r="I28" s="86" t="s">
         <v>191</v>
       </c>
-      <c r="J28" s="185">
+      <c r="J28" s="84">
         <v>3123932302</v>
       </c>
-      <c r="K28" s="187" t="s">
+      <c r="K28" s="86" t="s">
         <v>192</v>
       </c>
       <c r="L28" s="48"/>
@@ -42736,32 +42946,32 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B29" s="188" t="s">
+      <c r="B29" s="87" t="s">
         <v>193</v>
       </c>
-      <c r="C29" s="189" t="s">
+      <c r="C29" s="88" t="s">
         <v>92</v>
       </c>
-      <c r="D29" s="188">
+      <c r="D29" s="87">
         <v>1028944741</v>
       </c>
-      <c r="E29" s="190"/>
-      <c r="F29" s="190" t="s">
+      <c r="E29" s="89"/>
+      <c r="F29" s="89" t="s">
         <v>194</v>
       </c>
-      <c r="G29" s="188">
+      <c r="G29" s="87">
         <v>3249400317</v>
       </c>
-      <c r="H29" s="188" t="s">
+      <c r="H29" s="87" t="s">
         <v>195</v>
       </c>
-      <c r="I29" s="190" t="s">
+      <c r="I29" s="89" t="s">
         <v>196</v>
       </c>
-      <c r="J29" s="188">
+      <c r="J29" s="87">
         <v>3229630361</v>
       </c>
-      <c r="K29" s="190" t="s">
+      <c r="K29" s="89" t="s">
         <v>197</v>
       </c>
       <c r="L29" s="48"/>
@@ -42785,32 +42995,32 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B30" s="185" t="s">
+      <c r="B30" s="84" t="s">
         <v>198</v>
       </c>
-      <c r="C30" s="186" t="s">
+      <c r="C30" s="85" t="s">
         <v>92</v>
       </c>
-      <c r="D30" s="185">
+      <c r="D30" s="84">
         <v>1016955950</v>
       </c>
-      <c r="E30" s="187"/>
-      <c r="F30" s="187" t="s">
+      <c r="E30" s="86"/>
+      <c r="F30" s="86" t="s">
         <v>199</v>
       </c>
-      <c r="G30" s="185">
+      <c r="G30" s="84">
         <v>3124387321</v>
       </c>
-      <c r="H30" s="185" t="s">
+      <c r="H30" s="84" t="s">
         <v>200</v>
       </c>
-      <c r="I30" s="187" t="s">
+      <c r="I30" s="86" t="s">
         <v>201</v>
       </c>
-      <c r="J30" s="185">
+      <c r="J30" s="84">
         <v>3107937846</v>
       </c>
-      <c r="K30" s="187" t="s">
+      <c r="K30" s="86" t="s">
         <v>202</v>
       </c>
       <c r="L30" s="48"/>
@@ -42834,32 +43044,32 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B31" s="188" t="s">
+      <c r="B31" s="87" t="s">
         <v>203</v>
       </c>
-      <c r="C31" s="189" t="s">
+      <c r="C31" s="88" t="s">
         <v>92</v>
       </c>
-      <c r="D31" s="188">
+      <c r="D31" s="87">
         <v>1013648077</v>
       </c>
-      <c r="E31" s="190"/>
-      <c r="F31" s="190" t="s">
+      <c r="E31" s="89"/>
+      <c r="F31" s="89" t="s">
         <v>204</v>
       </c>
-      <c r="G31" s="188">
+      <c r="G31" s="87">
         <v>3052031244</v>
       </c>
-      <c r="H31" s="188" t="s">
+      <c r="H31" s="87" t="s">
         <v>205</v>
       </c>
-      <c r="I31" s="190" t="s">
+      <c r="I31" s="89" t="s">
         <v>206</v>
       </c>
-      <c r="J31" s="188">
+      <c r="J31" s="87">
         <v>3144924776</v>
       </c>
-      <c r="K31" s="190" t="s">
+      <c r="K31" s="89" t="s">
         <v>207</v>
       </c>
       <c r="L31" s="59"/>
@@ -42883,32 +43093,32 @@
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B32" s="185" t="s">
+      <c r="B32" s="84" t="s">
         <v>208</v>
       </c>
-      <c r="C32" s="186" t="s">
+      <c r="C32" s="85" t="s">
         <v>92</v>
       </c>
-      <c r="D32" s="185">
+      <c r="D32" s="84">
         <v>1070393748</v>
       </c>
-      <c r="E32" s="187"/>
-      <c r="F32" s="187" t="s">
+      <c r="E32" s="86"/>
+      <c r="F32" s="86" t="s">
         <v>209</v>
       </c>
-      <c r="G32" s="185">
+      <c r="G32" s="84">
         <v>3226834395</v>
       </c>
-      <c r="H32" s="185" t="s">
+      <c r="H32" s="84" t="s">
         <v>210</v>
       </c>
-      <c r="I32" s="187" t="s">
+      <c r="I32" s="86" t="s">
         <v>211</v>
       </c>
-      <c r="J32" s="185">
+      <c r="J32" s="84">
         <v>3153966851</v>
       </c>
-      <c r="K32" s="187" t="s">
+      <c r="K32" s="86" t="s">
         <v>212</v>
       </c>
       <c r="L32" s="59"/>
@@ -42932,32 +43142,32 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B33" s="188" t="s">
+      <c r="B33" s="87" t="s">
         <v>213</v>
       </c>
-      <c r="C33" s="189" t="s">
+      <c r="C33" s="88" t="s">
         <v>125</v>
       </c>
-      <c r="D33" s="188">
+      <c r="D33" s="87">
         <v>1016953617</v>
       </c>
-      <c r="E33" s="190"/>
-      <c r="F33" s="190" t="s">
+      <c r="E33" s="89"/>
+      <c r="F33" s="89" t="s">
         <v>214</v>
       </c>
-      <c r="G33" s="188">
+      <c r="G33" s="87">
         <v>3215875958</v>
       </c>
-      <c r="H33" s="188" t="s">
+      <c r="H33" s="87" t="s">
         <v>215</v>
       </c>
-      <c r="I33" s="190" t="s">
+      <c r="I33" s="89" t="s">
         <v>216</v>
       </c>
-      <c r="J33" s="188">
+      <c r="J33" s="87">
         <v>3117650209</v>
       </c>
-      <c r="K33" s="190" t="s">
+      <c r="K33" s="89" t="s">
         <v>217</v>
       </c>
       <c r="L33" s="48"/>
@@ -42981,32 +43191,32 @@
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B34" s="185" t="s">
+      <c r="B34" s="84" t="s">
         <v>218</v>
       </c>
-      <c r="C34" s="186" t="s">
+      <c r="C34" s="85" t="s">
         <v>92</v>
       </c>
-      <c r="D34" s="185">
+      <c r="D34" s="84">
         <v>1030580520</v>
       </c>
-      <c r="E34" s="187"/>
-      <c r="F34" s="187" t="s">
+      <c r="E34" s="86"/>
+      <c r="F34" s="86" t="s">
         <v>219</v>
       </c>
-      <c r="G34" s="185">
+      <c r="G34" s="84">
         <v>3112167570</v>
       </c>
-      <c r="H34" s="185" t="s">
+      <c r="H34" s="84" t="s">
         <v>220</v>
       </c>
-      <c r="I34" s="187" t="s">
+      <c r="I34" s="86" t="s">
         <v>221</v>
       </c>
-      <c r="J34" s="185">
+      <c r="J34" s="84">
         <v>3104862895</v>
       </c>
-      <c r="K34" s="187" t="s">
+      <c r="K34" s="86" t="s">
         <v>222</v>
       </c>
       <c r="L34" s="48"/>
@@ -43032,30 +43242,30 @@
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B35" s="188" t="s">
+      <c r="B35" s="87" t="s">
         <v>223</v>
       </c>
-      <c r="C35" s="189" t="s">
+      <c r="C35" s="88" t="s">
         <v>92</v>
       </c>
-      <c r="D35" s="188">
+      <c r="D35" s="87">
         <v>1014877985</v>
       </c>
-      <c r="E35" s="190"/>
-      <c r="F35" s="190" t="s">
+      <c r="E35" s="89"/>
+      <c r="F35" s="89" t="s">
         <v>224</v>
       </c>
-      <c r="G35" s="188">
+      <c r="G35" s="87">
         <v>3223439173</v>
       </c>
-      <c r="H35" s="188" t="s">
+      <c r="H35" s="87" t="s">
         <v>225</v>
       </c>
-      <c r="I35" s="190"/>
-      <c r="J35" s="188">
+      <c r="I35" s="89"/>
+      <c r="J35" s="87">
         <v>3142202285</v>
       </c>
-      <c r="K35" s="190" t="s">
+      <c r="K35" s="89" t="s">
         <v>226</v>
       </c>
       <c r="L35" s="48"/>
@@ -43079,32 +43289,32 @@
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="B36" s="185" t="s">
+      <c r="B36" s="84" t="s">
         <v>227</v>
       </c>
-      <c r="C36" s="186" t="s">
+      <c r="C36" s="85" t="s">
         <v>92</v>
       </c>
-      <c r="D36" s="185">
+      <c r="D36" s="84">
         <v>1141718299</v>
       </c>
-      <c r="E36" s="187"/>
-      <c r="F36" s="187" t="s">
+      <c r="E36" s="86"/>
+      <c r="F36" s="86" t="s">
         <v>228</v>
       </c>
-      <c r="G36" s="185">
+      <c r="G36" s="84">
         <v>3505962031</v>
       </c>
-      <c r="H36" s="185" t="s">
+      <c r="H36" s="84" t="s">
         <v>229</v>
       </c>
-      <c r="I36" s="187" t="s">
+      <c r="I36" s="86" t="s">
         <v>230</v>
       </c>
-      <c r="J36" s="185">
+      <c r="J36" s="84">
         <v>3118784119</v>
       </c>
-      <c r="K36" s="187" t="s">
+      <c r="K36" s="86" t="s">
         <v>231</v>
       </c>
       <c r="L36" s="48"/>
@@ -43128,32 +43338,32 @@
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="B37" s="188" t="s">
+      <c r="B37" s="87" t="s">
         <v>232</v>
       </c>
-      <c r="C37" s="189" t="s">
+      <c r="C37" s="88" t="s">
         <v>125</v>
       </c>
-      <c r="D37" s="188">
+      <c r="D37" s="87">
         <v>1016950671</v>
       </c>
-      <c r="E37" s="190"/>
-      <c r="F37" s="190" t="s">
+      <c r="E37" s="89"/>
+      <c r="F37" s="89" t="s">
         <v>233</v>
       </c>
-      <c r="G37" s="188">
+      <c r="G37" s="87">
         <v>3012119395</v>
       </c>
-      <c r="H37" s="188" t="s">
+      <c r="H37" s="87" t="s">
         <v>234</v>
       </c>
-      <c r="I37" s="190" t="s">
+      <c r="I37" s="89" t="s">
         <v>235</v>
       </c>
-      <c r="J37" s="188">
+      <c r="J37" s="87">
         <v>3144034180</v>
       </c>
-      <c r="K37" s="190" t="s">
+      <c r="K37" s="89" t="s">
         <v>236</v>
       </c>
       <c r="L37" s="48"/>
@@ -43177,32 +43387,32 @@
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="B38" s="185" t="s">
+      <c r="B38" s="84" t="s">
         <v>237</v>
       </c>
-      <c r="C38" s="186" t="s">
+      <c r="C38" s="85" t="s">
         <v>92</v>
       </c>
-      <c r="D38" s="185">
+      <c r="D38" s="84">
         <v>1025147204</v>
       </c>
-      <c r="E38" s="187"/>
-      <c r="F38" s="187" t="s">
+      <c r="E38" s="86"/>
+      <c r="F38" s="86" t="s">
         <v>238</v>
       </c>
-      <c r="G38" s="185">
+      <c r="G38" s="84">
         <v>3134549827</v>
       </c>
-      <c r="H38" s="185" t="s">
+      <c r="H38" s="84" t="s">
         <v>239</v>
       </c>
-      <c r="I38" s="187" t="s">
+      <c r="I38" s="86" t="s">
         <v>240</v>
       </c>
-      <c r="J38" s="185">
+      <c r="J38" s="84">
         <v>3214467031</v>
       </c>
-      <c r="K38" s="187" t="s">
+      <c r="K38" s="86" t="s">
         <v>241</v>
       </c>
       <c r="L38" s="48"/>
@@ -43228,32 +43438,32 @@
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="B39" s="188" t="s">
+      <c r="B39" s="87" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="189" t="s">
+      <c r="C39" s="88" t="s">
         <v>92</v>
       </c>
-      <c r="D39" s="188">
+      <c r="D39" s="87">
         <v>1014236875</v>
       </c>
-      <c r="E39" s="190"/>
-      <c r="F39" s="190" t="s">
+      <c r="E39" s="89"/>
+      <c r="F39" s="89" t="s">
         <v>243</v>
       </c>
-      <c r="G39" s="188">
+      <c r="G39" s="87">
         <v>3118236873</v>
       </c>
-      <c r="H39" s="188" t="s">
+      <c r="H39" s="87" t="s">
         <v>244</v>
       </c>
-      <c r="I39" s="190" t="s">
+      <c r="I39" s="89" t="s">
         <v>243</v>
       </c>
-      <c r="J39" s="188">
+      <c r="J39" s="87">
         <v>3115512588</v>
       </c>
-      <c r="K39" s="190" t="s">
+      <c r="K39" s="89" t="s">
         <v>245</v>
       </c>
       <c r="L39" s="48"/>
@@ -43279,32 +43489,32 @@
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B40" s="185" t="s">
+      <c r="B40" s="84" t="s">
         <v>246</v>
       </c>
-      <c r="C40" s="186" t="s">
+      <c r="C40" s="85" t="s">
         <v>92</v>
       </c>
-      <c r="D40" s="185">
+      <c r="D40" s="84">
         <v>1141122555</v>
       </c>
-      <c r="E40" s="187"/>
-      <c r="F40" s="187" t="s">
+      <c r="E40" s="86"/>
+      <c r="F40" s="86" t="s">
         <v>247</v>
       </c>
-      <c r="G40" s="185">
+      <c r="G40" s="84">
         <v>3202525512</v>
       </c>
-      <c r="H40" s="185" t="s">
+      <c r="H40" s="84" t="s">
         <v>248</v>
       </c>
-      <c r="I40" s="187" t="s">
+      <c r="I40" s="86" t="s">
         <v>249</v>
       </c>
-      <c r="J40" s="185">
+      <c r="J40" s="84">
         <v>3134800188</v>
       </c>
-      <c r="K40" s="187" t="s">
+      <c r="K40" s="86" t="s">
         <v>250</v>
       </c>
       <c r="L40" s="48"/>
@@ -43328,32 +43538,32 @@
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="B41" s="188" t="s">
+      <c r="B41" s="87" t="s">
         <v>251</v>
       </c>
-      <c r="C41" s="189" t="s">
+      <c r="C41" s="88" t="s">
         <v>92</v>
       </c>
-      <c r="D41" s="188">
+      <c r="D41" s="87">
         <v>1019766073</v>
       </c>
-      <c r="E41" s="190"/>
-      <c r="F41" s="190" t="s">
+      <c r="E41" s="89"/>
+      <c r="F41" s="89" t="s">
         <v>252</v>
       </c>
-      <c r="G41" s="188">
+      <c r="G41" s="87">
         <v>3005099320</v>
       </c>
-      <c r="H41" s="188" t="s">
+      <c r="H41" s="87" t="s">
         <v>253</v>
       </c>
-      <c r="I41" s="190" t="s">
+      <c r="I41" s="89" t="s">
         <v>254</v>
       </c>
-      <c r="J41" s="188">
+      <c r="J41" s="87">
         <v>3108173065</v>
       </c>
-      <c r="K41" s="190" t="s">
+      <c r="K41" s="89" t="s">
         <v>255</v>
       </c>
       <c r="L41" s="48"/>
@@ -43377,32 +43587,32 @@
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="B42" s="185" t="s">
+      <c r="B42" s="84" t="s">
         <v>256</v>
       </c>
-      <c r="C42" s="186" t="s">
+      <c r="C42" s="85" t="s">
         <v>92</v>
       </c>
-      <c r="D42" s="185">
+      <c r="D42" s="84">
         <v>1014238500</v>
       </c>
-      <c r="E42" s="187"/>
-      <c r="F42" s="187" t="s">
+      <c r="E42" s="86"/>
+      <c r="F42" s="86" t="s">
         <v>257</v>
       </c>
-      <c r="G42" s="185">
+      <c r="G42" s="84">
         <v>3213759951</v>
       </c>
-      <c r="H42" s="185" t="s">
+      <c r="H42" s="84" t="s">
         <v>258</v>
       </c>
-      <c r="I42" s="187" t="s">
+      <c r="I42" s="86" t="s">
         <v>259</v>
       </c>
-      <c r="J42" s="185">
+      <c r="J42" s="84">
         <v>3113378282</v>
       </c>
-      <c r="K42" s="187" t="s">
+      <c r="K42" s="86" t="s">
         <v>260</v>
       </c>
       <c r="L42" s="48"/>
@@ -43428,32 +43638,32 @@
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="B43" s="188" t="s">
+      <c r="B43" s="87" t="s">
         <v>261</v>
       </c>
-      <c r="C43" s="189" t="s">
+      <c r="C43" s="88" t="s">
         <v>92</v>
       </c>
-      <c r="D43" s="188">
+      <c r="D43" s="87">
         <v>1146126178</v>
       </c>
-      <c r="E43" s="190"/>
-      <c r="F43" s="190" t="s">
+      <c r="E43" s="89"/>
+      <c r="F43" s="89" t="s">
         <v>262</v>
       </c>
-      <c r="G43" s="188">
+      <c r="G43" s="87">
         <v>3187175748</v>
       </c>
-      <c r="H43" s="188" t="s">
+      <c r="H43" s="87" t="s">
         <v>263</v>
       </c>
-      <c r="I43" s="190" t="s">
+      <c r="I43" s="89" t="s">
         <v>264</v>
       </c>
-      <c r="J43" s="188">
+      <c r="J43" s="87">
         <v>3205935369</v>
       </c>
-      <c r="K43" s="190" t="s">
+      <c r="K43" s="89" t="s">
         <v>265</v>
       </c>
       <c r="L43" s="48"/>
@@ -43473,36 +43683,36 @@
       <c r="Z43" s="48"/>
     </row>
     <row r="44" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A44" s="183">
+      <c r="A44" s="82">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="B44" s="185" t="s">
+      <c r="B44" s="84" t="s">
         <v>266</v>
       </c>
-      <c r="C44" s="186" t="s">
+      <c r="C44" s="85" t="s">
         <v>92</v>
       </c>
-      <c r="D44" s="185">
+      <c r="D44" s="84">
         <v>1052842832</v>
       </c>
-      <c r="E44" s="187"/>
-      <c r="F44" s="187" t="s">
+      <c r="E44" s="86"/>
+      <c r="F44" s="86" t="s">
         <v>267</v>
       </c>
-      <c r="G44" s="185">
+      <c r="G44" s="84">
         <v>3143774905</v>
       </c>
-      <c r="H44" s="185" t="s">
+      <c r="H44" s="84" t="s">
         <v>268</v>
       </c>
-      <c r="I44" s="187" t="s">
+      <c r="I44" s="86" t="s">
         <v>269</v>
       </c>
-      <c r="J44" s="185">
+      <c r="J44" s="84">
         <v>3223845320</v>
       </c>
-      <c r="K44" s="187" t="s">
+      <c r="K44" s="86" t="s">
         <v>270</v>
       </c>
       <c r="L44" s="48"/>
@@ -43522,24 +43732,24 @@
       <c r="Z44" s="48"/>
     </row>
     <row r="45" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A45" s="183">
+      <c r="A45" s="82">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="B45" s="188" t="s">
+      <c r="B45" s="87" t="s">
         <v>271</v>
       </c>
-      <c r="C45" s="189"/>
-      <c r="D45" s="188">
+      <c r="C45" s="88"/>
+      <c r="D45" s="87">
         <v>1141123709</v>
       </c>
-      <c r="E45" s="190"/>
-      <c r="F45" s="190"/>
-      <c r="G45" s="188"/>
-      <c r="H45" s="188"/>
-      <c r="I45" s="190"/>
-      <c r="J45" s="188"/>
-      <c r="K45" s="190"/>
+      <c r="E45" s="89"/>
+      <c r="F45" s="89"/>
+      <c r="G45" s="87"/>
+      <c r="H45" s="87"/>
+      <c r="I45" s="89"/>
+      <c r="J45" s="87"/>
+      <c r="K45" s="89"/>
       <c r="L45" s="48"/>
       <c r="M45" s="48"/>
       <c r="N45" s="48"/>
@@ -43557,35 +43767,35 @@
       <c r="Z45" s="48"/>
     </row>
     <row r="46" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A46" s="184">
+      <c r="A46" s="83">
         <v>37</v>
       </c>
-      <c r="B46" s="185" t="s">
+      <c r="B46" s="84" t="s">
         <v>272</v>
       </c>
-      <c r="C46" s="186" t="s">
+      <c r="C46" s="85" t="s">
         <v>92</v>
       </c>
-      <c r="D46" s="185">
+      <c r="D46" s="84">
         <v>1141123427</v>
       </c>
-      <c r="E46" s="187"/>
-      <c r="F46" s="187" t="s">
+      <c r="E46" s="86"/>
+      <c r="F46" s="86" t="s">
         <v>273</v>
       </c>
-      <c r="G46" s="185">
+      <c r="G46" s="84">
         <v>3009750929</v>
       </c>
-      <c r="H46" s="185" t="s">
+      <c r="H46" s="84" t="s">
         <v>274</v>
       </c>
-      <c r="I46" s="187" t="s">
+      <c r="I46" s="86" t="s">
         <v>275</v>
       </c>
-      <c r="J46" s="185">
+      <c r="J46" s="84">
         <v>3124715955</v>
       </c>
-      <c r="K46" s="187" t="s">
+      <c r="K46" s="86" t="s">
         <v>276</v>
       </c>
       <c r="L46" s="61"/>
@@ -43607,35 +43817,35 @@
       <c r="Z46" s="61"/>
     </row>
     <row r="47" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A47" s="184">
+      <c r="A47" s="83">
         <v>38</v>
       </c>
-      <c r="B47" s="188" t="s">
+      <c r="B47" s="87" t="s">
         <v>277</v>
       </c>
-      <c r="C47" s="189" t="s">
+      <c r="C47" s="88" t="s">
         <v>92</v>
       </c>
-      <c r="D47" s="188">
+      <c r="D47" s="87">
         <v>1145225610</v>
       </c>
-      <c r="E47" s="190"/>
-      <c r="F47" s="190" t="s">
+      <c r="E47" s="89"/>
+      <c r="F47" s="89" t="s">
         <v>278</v>
       </c>
-      <c r="G47" s="188">
+      <c r="G47" s="87">
         <v>3239062253</v>
       </c>
-      <c r="H47" s="188" t="s">
+      <c r="H47" s="87" t="s">
         <v>279</v>
       </c>
-      <c r="I47" s="190" t="s">
+      <c r="I47" s="89" t="s">
         <v>280</v>
       </c>
-      <c r="J47" s="188">
+      <c r="J47" s="87">
         <v>3104848424</v>
       </c>
-      <c r="K47" s="190" t="s">
+      <c r="K47" s="89" t="s">
         <v>281</v>
       </c>
       <c r="L47" s="48"/>
@@ -52354,12 +52564,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" customHeight="1">
-      <c r="A1" s="169" t="s">
+      <c r="A1" s="190" t="s">
         <v>81</v>
       </c>
-      <c r="B1" s="93"/>
-      <c r="C1" s="93"/>
-      <c r="D1" s="93"/>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
       <c r="E1" s="62"/>
       <c r="F1" s="62"/>
     </row>
@@ -52378,7 +52588,7 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="15.75">
-      <c r="A3" s="166" t="s">
+      <c r="A3" s="187" t="s">
         <v>86</v>
       </c>
       <c r="B3" s="66"/>
@@ -52386,25 +52596,25 @@
       <c r="D3" s="67"/>
     </row>
     <row r="4" spans="1:6" ht="15.75">
-      <c r="A4" s="167"/>
+      <c r="A4" s="188"/>
       <c r="B4" s="66"/>
       <c r="C4" s="66"/>
       <c r="D4" s="67"/>
     </row>
     <row r="5" spans="1:6" ht="15.75">
-      <c r="A5" s="167"/>
+      <c r="A5" s="188"/>
       <c r="B5" s="66"/>
       <c r="C5" s="66"/>
       <c r="D5" s="67"/>
     </row>
     <row r="6" spans="1:6" ht="15.75">
-      <c r="A6" s="167"/>
+      <c r="A6" s="188"/>
       <c r="B6" s="66"/>
       <c r="C6" s="66"/>
       <c r="D6" s="67"/>
     </row>
     <row r="7" spans="1:6" ht="15.75">
-      <c r="A7" s="168"/>
+      <c r="A7" s="189"/>
       <c r="B7" s="68"/>
       <c r="C7" s="68"/>
       <c r="D7" s="69"/>
@@ -52427,7 +52637,7 @@
       </c>
     </row>
     <row r="10" spans="1:6" ht="15.75">
-      <c r="A10" s="166" t="s">
+      <c r="A10" s="187" t="s">
         <v>86</v>
       </c>
       <c r="B10" s="66"/>
@@ -52435,25 +52645,25 @@
       <c r="D10" s="67"/>
     </row>
     <row r="11" spans="1:6" ht="15.75">
-      <c r="A11" s="167"/>
+      <c r="A11" s="188"/>
       <c r="B11" s="66"/>
       <c r="C11" s="66"/>
       <c r="D11" s="67"/>
     </row>
     <row r="12" spans="1:6" ht="15.75">
-      <c r="A12" s="167"/>
+      <c r="A12" s="188"/>
       <c r="B12" s="66"/>
       <c r="C12" s="66"/>
       <c r="D12" s="67"/>
     </row>
     <row r="13" spans="1:6" ht="15.75">
-      <c r="A13" s="167"/>
+      <c r="A13" s="188"/>
       <c r="B13" s="66"/>
       <c r="C13" s="66"/>
       <c r="D13" s="67"/>
     </row>
     <row r="14" spans="1:6" ht="15.75">
-      <c r="A14" s="168"/>
+      <c r="A14" s="189"/>
       <c r="B14" s="68"/>
       <c r="C14" s="68"/>
       <c r="D14" s="69"/>
@@ -52473,7 +52683,7 @@
       </c>
     </row>
     <row r="17" spans="1:4" ht="15.75">
-      <c r="A17" s="166" t="s">
+      <c r="A17" s="187" t="s">
         <v>86</v>
       </c>
       <c r="B17" s="66"/>
@@ -52481,25 +52691,25 @@
       <c r="D17" s="67"/>
     </row>
     <row r="18" spans="1:4" ht="15.75">
-      <c r="A18" s="167"/>
+      <c r="A18" s="188"/>
       <c r="B18" s="66"/>
       <c r="C18" s="66"/>
       <c r="D18" s="67"/>
     </row>
     <row r="19" spans="1:4" ht="15.75">
-      <c r="A19" s="167"/>
+      <c r="A19" s="188"/>
       <c r="B19" s="66"/>
       <c r="C19" s="66"/>
       <c r="D19" s="67"/>
     </row>
     <row r="20" spans="1:4" ht="15.75">
-      <c r="A20" s="167"/>
+      <c r="A20" s="188"/>
       <c r="B20" s="66"/>
       <c r="C20" s="66"/>
       <c r="D20" s="67"/>
     </row>
     <row r="21" spans="1:4" ht="15.75">
-      <c r="A21" s="168"/>
+      <c r="A21" s="189"/>
       <c r="B21" s="68"/>
       <c r="C21" s="68"/>
       <c r="D21" s="69"/>
@@ -52519,7 +52729,7 @@
       </c>
     </row>
     <row r="24" spans="1:4" ht="15.75">
-      <c r="A24" s="166" t="s">
+      <c r="A24" s="187" t="s">
         <v>86</v>
       </c>
       <c r="B24" s="66"/>
@@ -52527,25 +52737,25 @@
       <c r="D24" s="67"/>
     </row>
     <row r="25" spans="1:4" ht="15.75">
-      <c r="A25" s="167"/>
+      <c r="A25" s="188"/>
       <c r="B25" s="66"/>
       <c r="C25" s="66"/>
       <c r="D25" s="67"/>
     </row>
     <row r="26" spans="1:4" ht="15.75">
-      <c r="A26" s="167"/>
+      <c r="A26" s="188"/>
       <c r="B26" s="66"/>
       <c r="C26" s="66"/>
       <c r="D26" s="67"/>
     </row>
     <row r="27" spans="1:4" ht="15.75">
-      <c r="A27" s="167"/>
+      <c r="A27" s="188"/>
       <c r="B27" s="66"/>
       <c r="C27" s="66"/>
       <c r="D27" s="67"/>
     </row>
     <row r="28" spans="1:4" ht="15.75">
-      <c r="A28" s="168"/>
+      <c r="A28" s="189"/>
       <c r="B28" s="68"/>
       <c r="C28" s="68"/>
       <c r="D28" s="69"/>
@@ -52565,7 +52775,7 @@
       </c>
     </row>
     <row r="31" spans="1:4" ht="15.75">
-      <c r="A31" s="166" t="s">
+      <c r="A31" s="187" t="s">
         <v>86</v>
       </c>
       <c r="B31" s="66"/>
@@ -52573,25 +52783,25 @@
       <c r="D31" s="67"/>
     </row>
     <row r="32" spans="1:4" ht="15.75">
-      <c r="A32" s="167"/>
+      <c r="A32" s="188"/>
       <c r="B32" s="66"/>
       <c r="C32" s="66"/>
       <c r="D32" s="67"/>
     </row>
     <row r="33" spans="1:4" ht="15.75">
-      <c r="A33" s="167"/>
+      <c r="A33" s="188"/>
       <c r="B33" s="66"/>
       <c r="C33" s="66"/>
       <c r="D33" s="67"/>
     </row>
     <row r="34" spans="1:4" ht="15.75">
-      <c r="A34" s="167"/>
+      <c r="A34" s="188"/>
       <c r="B34" s="66"/>
       <c r="C34" s="66"/>
       <c r="D34" s="67"/>
     </row>
     <row r="35" spans="1:4" ht="15.75">
-      <c r="A35" s="168"/>
+      <c r="A35" s="189"/>
       <c r="B35" s="68"/>
       <c r="C35" s="68"/>
       <c r="D35" s="69"/>
@@ -52611,7 +52821,7 @@
       </c>
     </row>
     <row r="38" spans="1:4" ht="15.75">
-      <c r="A38" s="166" t="s">
+      <c r="A38" s="187" t="s">
         <v>86</v>
       </c>
       <c r="B38" s="66"/>
@@ -52619,25 +52829,25 @@
       <c r="D38" s="67"/>
     </row>
     <row r="39" spans="1:4" ht="15.75">
-      <c r="A39" s="167"/>
+      <c r="A39" s="188"/>
       <c r="B39" s="66"/>
       <c r="C39" s="66"/>
       <c r="D39" s="67"/>
     </row>
     <row r="40" spans="1:4" ht="15.75">
-      <c r="A40" s="167"/>
+      <c r="A40" s="188"/>
       <c r="B40" s="66"/>
       <c r="C40" s="66"/>
       <c r="D40" s="67"/>
     </row>
     <row r="41" spans="1:4" ht="15.75">
-      <c r="A41" s="167"/>
+      <c r="A41" s="188"/>
       <c r="B41" s="66"/>
       <c r="C41" s="66"/>
       <c r="D41" s="67"/>
     </row>
     <row r="42" spans="1:4" ht="15.75">
-      <c r="A42" s="168"/>
+      <c r="A42" s="189"/>
       <c r="B42" s="68"/>
       <c r="C42" s="68"/>
       <c r="D42" s="69"/>
